--- a/prospeccao_juridica/RENDA_EXTRA_CONTATOS.xlsx
+++ b/prospeccao_juridica/RENDA_EXTRA_CONTATOS.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RENDA EXTRA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CONTATOS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RENDA EXTRA'!$A$1:$L$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CONTATOS'!$A$1:$L$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +40,7 @@
       <color rgb="001F3864"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -54,7 +54,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,16 +80,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -119,10 +124,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -138,6 +143,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -505,10 +513,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -518,7 +526,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
     <col width="78" customWidth="1" min="10" max="10"/>
-    <col width="90" customWidth="1" min="11" max="11"/>
+    <col width="92" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -584,56 +592,56 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ADVBOX</t>
+          <t>FUNCEF - Credenciamento de Escritórios de Advocacia</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Florianópolis</t>
+          <t>Brasília</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>relacionamento@advbox.com.br</t>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>credenciamentojuridico@funcef.com.br</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Cadastro / parceria / trabalhe conosco</t>
+          <t>CREDENCIAMENTO formal para contencioso de massa</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.advbox.com.br/</t>
+          <t>https://www.funcef.com.br/credenciamento-escritorios-advocacia/</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Square Corporate Center, Sala 226, Florianopolis/SC | CNPJ 30.750.260/0001-45</t>
+          <t>Texto do site: "O canal EXCLUSIVO para tratar de assuntos relativos ao processo de credenciamento e o e-mail credenciamentojuridico@funcef.com.br" | 0800 706 9000 | SCN Q2 Bl A, Ed. Corporate Financial Center, Brasilia-DF</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Legaltech de gestao e CONTROLADORIA JURIDICA com base de escritorios clientes. Tem pagina TRABALHE CONOSCO. Porta de entrada para a rede de escritorios que usam a plataforma.</t>
+          <t>MELHOR LEAD INSTITUCIONAL DA BASE. Credenciamento com vigencia de 12 meses, renovavel. A propria pagina avisa que a contratacao nao garante acionamento - mas estar credenciado e pre-requisito. Se faltar documento, dao 5 dias uteis para regularizar. Credenciam por AREA, inclusive contencioso de massa.</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -642,131 +650,131 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
+    <row r="3" ht="62" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Diligeiro (Tikal Tech)</t>
+          <t>Aval (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>contato@tikal.tech</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>0800 770 1516 / 0800 721 7091</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Cadastro na rede de correspondentes</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://www.diligeiro.com.br/</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Av. Queiroz Filho, 1700, Sao Paulo/SP | CNPJ 22.125.577/0001-62</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Rede de profissionais do Direito com oportunidades de servico EM TODO O BRASIL. Site em manutencao, mas o formulario de contato esta ativo - deixe nome, e-mail, WhatsApp e mensagem.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="62" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>LS Correspondente Jurídico</t>
+          <t>BP Gestão (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>contato@lscorrespondentejuridico.com.br</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>0800 643 9298 / 0800 721 9292</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Cadastro no banco de correspondentes - parceria autonoma</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://lscorrespondentejuridico.com.br/seja-nosso-parceiro/</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Celular 92 98109-9962 | Rua 25, 982, Parque Dez de Novembro, Manaus/AM, CEP 69055-430</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>PAGINA "SEJA NOSSO PARCEIRO" com texto expresso: buscam alianca com advogados nao efetivos, em regime AUTONOMO e NAO EXCLUSIVO, encaminhando servicos de correspondente e clientes para trabalho conjunto. Regiao Norte.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Meu Correspondente Jurídico (Activeline)</t>
+          <t>Cardoso &amp; Corrêa (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -779,110 +787,110 @@
           <t>BR</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>contato@activeline.com.br</t>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>0800 603 6680</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Cadastro gratuito como correspondente em RO</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://meucorrespondentejuridico.com.br/</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Cadastro TOTALMENTE GRATUITO, sem taxas. Abrangencia de comarcas definida por voce, ilimitada. Notificacoes de demanda por e-mail, telefone ou WhatsApp.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>JurisConnect</t>
+          <t>Concentrix Services (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>WHATSAPP</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>(11) 98201-4321</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>0800 645 2902</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Cadastro como correspondente - sem mensalidade</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://www.jurisconnect.com.br/</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Tel e WhatsApp (11) 98201-4321 | JurisConnect Ltda</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>CADASTRO GRATUITO, SEM MENSALIDADE - paga-se por demanda executada. Numeros do proprio site (14/09/2026): 3.044 demandas em 12 meses, 2.669 concluidas, 988 correspondentes com OAB. Tem pagina propria de cadastro de correspondente.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="62" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nosso Direito - Diretório de Parceiros</t>
+          <t>Concilig (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -897,50 +905,50 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>https://nossodireito.com/parceiros</t>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>0800 2020 308 / 0800 404 0100</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Cadastro gratuito no diretorio previdenciario nacional</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://nossodireito.com/parceiros</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Formulario pede: nome, OAB, email, WhatsApp, cidade, UF, area principal e volume mensal de casos</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>RENDA EXTRA DIRETA: cadastro GRATUITO, ABRANGENCIA NACIONAL, conecta REQUERENTES PREVIDENCIARIOS de todo o pais a advogados. Previdenciario e sua area principal. Faca hoje.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Radar Gestão para Advogados - Banco de Talentos</t>
+          <t>DivZero (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -955,50 +963,50 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>https://radardagestao.com.br/vagas</t>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>0800 000 0375 / 0800 000 8284</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Cadastro no banco de talentos - vagas remotas nacionais</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://radardagestao.com.br/vagas</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>"Cadastre-se em nosso Banco de Talentos" | Recrutam para escritorios e departamentos juridicos em TODO O TERRITORIO NACIONAL, vagas presenciais E REMOTAS</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Recrutadora especializada so em juridico. Cadastro no banco de talentos alimenta vagas remotas de todo o pais.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Brasil Correspondentes</t>
+          <t>Funchal (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1011,52 +1019,52 @@
           <t>BR</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>https://www.brasilcorrespondentes.com.br/</t>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>0800 770 8885 / (11) 3508-4794</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Cadastro como correspondente</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://www.brasilcorrespondentes.com.br/</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Planos a partir de R$ 14,98/mes</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Cadastro permite oferecer servicos em ate 3 cidades. Contato direto entre as partes, sem intermediario.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Correspondente.com.br</t>
+          <t>H. Costa (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1069,52 +1077,52 @@
           <t>BR</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>https://correspondente.com.br/</t>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>0800 941 9296 / 0800 941 9294</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Cadastro como prestador na plataforma</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://correspondente.com.br/</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Rede de mais de 20 mil prestadores. Fornece advogados para audiencias trabalhistas e civeis, presenciais e virtuais, alem de diligencias e protocolos.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="62" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Correspondentes na Web</t>
+          <t>JCS (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1127,110 +1135,110 @@
           <t>BR</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>https://correspondentesnaweb.com.br/cadastro.html</t>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>0800 600 5020 / 0800 600 1106</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Cadastro gratuito como correspondente</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://correspondentesnaweb.com.br/cadastro.html</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CNPJ 19.770.735/0001-22</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>CADASTRO BASICO GRATUITO. No formulario da para marcar os servicos: copias e protocolos, audiencias, e servicos em cartorios e prefeitura.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>GetNinjas</t>
+          <t>João Barbosa (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>https://www.getninjas.com.br/</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>0800 941 7803 / (81) 2122-1600</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Cadastro como profissional (categoria Consultoria/Juridico)</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>https://www.getninjas.com.br/</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Rua Dr. Fernandes Coelho, 85, 3o andar, Sao Paulo/SP | CNPJ 55.744.877/0001-89</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Marketplace de servicos com area "Seja um profissional". Categoria Consultoria abrange servicos juridicos. Cliente vem por demanda.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Juris Correspondente</t>
+          <t>Kawasaki (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1243,168 +1251,168 @@
           <t>BR</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>https://www.juriscorrespondente.com.br/seja-correspondente-juridico</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>0800 880 1830 / 0800 726 7040</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Cadastro gratuito como correspondente</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>https://www.juriscorrespondente.com.br/seja-correspondente-juridico</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>CADASTRO BASICO GRATUITO, planos pagos so ampliam visibilidade. Qualquer advogado com OAB pode se cadastrar.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Jusbrasil - Diretório de Advogados</t>
+          <t>ML Gomes (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>https://www.jusbrasil.com.br/advogados</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>0800 888 0604 / 0800 888 3535</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Cadastro gratuito no diretorio nacional</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>https://www.jusbrasil.com.br/advogados</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>"E gratis e rapido se cadastrar"</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>RENDA EXTRA: maior portal juridico do pais. Cadastro GRATUITO no diretorio gera contato direto de clientes. Depoimento no proprio site: advogada relata atender 99% dos casos sem reuniao presencial, so por telefone.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="62" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Migalhas Correspondentes</t>
+          <t>Negocie Digital (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>https://correspondentes.migalhas.com.br/</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>(11) 4858-5151</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Cadastro como correspondente em RO</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>https://correspondentes.migalhas.com.br/</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Planos: R$ 47/mes (4 meses) ate R$ 28,58/mes (24 meses)</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>IMPORTANTE: tem secao "PRECISAMOS DE CORRESPONDENTES" listando as cidades com solicitacao de servico e SEM correspondente cadastrado. Vale checar se alguma comarca de RO esta nessa lista - entrada com demanda garantida.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="62" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Via Justa (Justto)</t>
+          <t>Paschoalotto (assessoria credenciada Bradesco)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1417,62 +1425,62 @@
           <t>BR</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>https://www.justto.com.br/</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>0800 400 8810 / 0800 400 0528</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Cadastro na area do advogado</t>
+          <t>Correspondencia, execucao e cobranca judicial nas comarcas de RO</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>https://www.justto.com.br/</t>
+          <t>https://banco.bradesco/html/classic/produtos-servicos/renegociacao-de-dividas/catalogo-de-assessorias.shtm</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>"Area do advogado: encontre oportunidades qualificadas compativeis com sua area de atuacao"</t>
+          <t>Consta do catalogo PUBLICO de empresas de cobranca credenciadas do Bradesco, com telefone e WhatsApp divulgados pelo proprio banco</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Plataforma que recebe o problema do cidadao, faz a triagem e encaminha para advogado. Verifica OAB. Nao exige que o advogado seja da cidade do cliente - serve para atuacao remota.</t>
+          <t>Assessoria de cobranca credenciada por banco de primeira linha. Cobranca amigavel vira execucao judicial - e ai precisam de advogado na comarca. Todas tem 0800, entao a ligacao e gratuita.</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1. PLATAFORMA — cadastre-se e receba demanda</t>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Workana</t>
+          <t>Agibank - Portal do Correspondente</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Campinas</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1480,30 +1488,30 @@
           <t>PORTAL</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>https://www.workana.com/pt</t>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>https://www.agibank.com.br/</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Cadastro como freelancer juridico</t>
+          <t>Cadastro no Portal do Correspondente</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>https://www.workana.com/pt</t>
+          <t>https://www.agibank.com.br/</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Workana LLC | recebimento em moeda local OU EM DOLAR</t>
+          <t>Tel 11 3004-2221 | SAC 0800 730 0999 | Rua Sergio Fernandes Borges Soares, 1000, Distrito Industrial, Campinas-SP | CNPJ 10.664.513/0001-50 | Menu traz "Portal do correspondente" e "Trabalhe com a gente"</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>RENDA EXTRA EM DOLAR: maior plataforma de freelance da America Latina. Projetos por objetivo ou por hora. Serve para elaboracao de pecas, pareceres e analise documental a distancia.</t>
+          <t>TOPO do ranking de litigiosidade por cliente da USP-RP: 2.156 acoes por 100 mil clientes, re em mais de 90% dos casos. Forte em consignado e BENEFICIO INSS - cruza com sua area previdenciaria. Tem PORTAL DO CORRESPONDENTE.</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1512,114 +1520,114 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>A Pioneira Administradora de Imóveis</t>
+          <t>BRB - Banco de Brasília - Portal do Fornecedor</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
+          <t>Brasília</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>apioneira.adm@hotmail.com</t>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>https://www.brb.com.br/</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Cobranca condominial, despejo, imobiliario</t>
+          <t>Cadastro no Portal do Fornecedor e acompanhamento de licitacoes</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>http://apioneira.adm.br/</t>
+          <t>https://www.brb.com.br/</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 3221-5292 / (69) 99247-1837 | R. Mal. Deodoro, 2949, Olaria, Porto Velho | e-mail alternativo: admin@apioneira.adm.br</t>
+          <t>Fale conosco (61) 3322-1515 | CNPJ 00.000.208/0001-00 | Centro Empresarial CNC, SAUN Q5 Lote C, Brasilia-DF | Menu com PORTAL DO FORNECEDOR e LICITACOES</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Dois e-mails publicados no site. Gestao de condominios residenciais e comerciais.</t>
+          <t>Banco publico: contratacao juridica passa por licitacao ou credenciamento formal. O Portal do Fornecedor e a porta de entrada. Consta do estudo da USP-RP entre os bancos de alta litigiosidade por cliente.</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>André Ragnini Sociedade de Advogados</t>
+          <t>Banco Daycoval - Canal do Correspondente</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Cacoal</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>contato@andreragnini.com.br</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>https://www.daycoval.com.br/</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Parceria entre escritorios e correspondencia</t>
+          <t>Cadastro no Canal do Correspondente</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>https://andreragnini.com.br/</t>
+          <t>https://www.daycoval.com.br/</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 99960-1224 | Av. Belo Horizonte, 2.297, Cacoal/RO | Dr. Andre Bonifacio Queiroz Ragnini</t>
+          <t>WhatsApp (11) 99111-6583 | CNPJ 62.232.889/0001-90 | Menu com "Canal do Correspondente", "Agencias e Correspondentes" e "Area Restrita para Agentes"</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>20+ anos em Cacoal. Atua em trabalhista, empresarial, tributario e previdenciario.</t>
+          <t>2o COLOCADO no ranking de litigiosidade por cliente da USP-RP (1.753 acoes por 100 mil clientes). Tem CANAL DO CORRESPONDENTE proprio no site - porta de entrada formal.</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1628,114 +1636,114 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="20" ht="62" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>BRD Advocacia &amp; Advogados Associados</t>
+          <t>Cresol</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Ariquemes</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Belnetobr@hotmail.com</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>https://www.cresol.com.br/</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Parceria entre escritorios e correspondencia</t>
+          <t>Cadastro / trabalhe conosco</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>https://www.brdadvocacia.com.br/</t>
+          <t>https://www.cresol.com.br/</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Dr. Belmiro Rogerio Duarte Bermudes Neto | Tel (69) 98482-4171 | Av. Guapore, 2628, Setor 05, Ariquemes/RO</t>
+          <t>Cartoes 4007-1600 e 0800 704 7500 | Ouvidoria/SAC/Denuncia 0800 643 1981 | PRESENTES EM 20 ESTADOS</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Ex-TJRO. Civel, previdenciario, trabalhista, criminal.</t>
+          <t>Cooperativa de credito presente em 20 estados, com forte atuacao no agro. Ja tem vaga juridica mapeada em Chapeco. Credito rural inadimplente vira execucao nas comarcas.</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>CDL Ji-Paraná - Câmara de Dirigentes Lojistas</t>
+          <t>Porto Seguro - Credenciamento de Advogados</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>saa@cdljp-ro.com.br</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.portoseguro.com.br/consulta-de-clientes/credenciamento-de-advogados</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Convenio de assessoria juridica para lojistas associados</t>
+          <t>Credenciamento de advogados</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>https://www.cdljipa.com.br/</t>
+          <t>https://www.portoseguro.com.br/consulta-de-clientes/credenciamento-de-advogados</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 3421-9772 / 3422-3385 | Travessa da CDL, 221, Centro, Ji-Parana</t>
+          <t>Pagina institucional dedicada. O site tem ainda areas para PRESTADORES DE SERVICO, FORNECEDORES e EDITAIS</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>NA SUA CIDADE. Cobranca e consumidor sao demanda recorrente dos lojistas.</t>
+          <t>3a maior seguradora do Brasil. Pagina permanente e especifica de CREDENCIAMENTO DE ADVOGADOS - nao depende de vaga aberta nem de relacionamento previo. Contencioso securitario e de automovel se espalha por todas as comarcas.</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1744,114 +1752,114 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="22" ht="62" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>1. CREDENCIAMENTO / CORRESPONDENTE DE BANCO — canal formal</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>CF Contabilidade - Ji-Paraná</t>
+          <t>Sicredi - Agente Credenciado</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>Porto Alegre</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>contato@cfjipa.com.br</t>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sicredi.com.br/</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Parceria juridica para a carteira de clientes PJ</t>
+          <t>Cadastro como agente credenciado</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>https://cfcontabilidade.com.br/unidades/jipa/</t>
+          <t>https://www.sicredi.com.br/</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Contato: Viviane Melo L. Tavares | Tel (69) 99367-6377 | Rua Manoel Franco, 840, Ji-Parana</t>
+          <t>Menu institucional traz AGENTE CREDENCIADO, Canal do consorciado e Trabalhe conosco</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>NA SUA CIDADE. Contabilidade desde 1989 - canal de indicacao de clientes empresariais.</t>
+          <t>Sistema cooperativo com mais de R$ 350 bilhoes em ativos e cooperativas singulares com autonomia. Tem canal formal de AGENTE CREDENCIADO. Credito rural gera execucao no interior.</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+          <t>Catalogo publico de assessorias credenciadas do Bradesco (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="62" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Expresso Rodotec (W S Transportes)</t>
+          <t>ADVBOX</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
+          <t>Florianópolis</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>contato@expressorodotec.com.br</t>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>relacionamento@advbox.com.br</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Assessoria trabalhista, tributaria e civel</t>
+          <t>Cadastro / parceria / trabalhe conosco</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>https://www.expressorodotec.com/</t>
+          <t>https://www.advbox.com.br/</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 9988-9359 | WhatsApp (69) 99952-8263 | Rua Jorubatuba, 6403, Aeroclube, Porto Velho-RO | CNPJ 15.186.966/0001-32</t>
+          <t>Square Corporate Center, Sala 226, Florianopolis/SC | CNPJ 30.750.260/0001-45</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>TEM PAGINA "SEJA PARCEIRO" E "TRABALHE CONOSCO" - dois canais de entrada. Clientes: DHL, Avon, Bemol.</t>
+          <t>Legaltech de gestao e CONTROLADORIA JURIDICA com base de escritorios clientes. Tem pagina TRABALHE CONOSCO. Porta de entrada para a rede de escritorios que usam a plataforma.</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1860,56 +1868,56 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="24" ht="62" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>FACER - Federação das Assoc. Comerciais e Empresariais de RO</t>
+          <t>Diligeiro (Tikal Tech)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>contato@facer.org.br</t>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>contato@tikal.tech</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Convenio de assessoria juridica para associados</t>
+          <t>Cadastro na rede de correspondentes</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>https://facer.org.br/institucional/sobre</t>
+          <t>https://www.diligeiro.com.br/</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 3229-8957 | Av. Calama 3250, Embratel, Porto Velho/RO</t>
+          <t>Av. Queiroz Filho, 1700, Sao Paulo/SP | CNPJ 22.125.577/0001-62</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>ALAVANCA MAXIMA: 31 associacoes comerciais, +7 mil empresas, 52 municipios de RO. Um convenio abre a base inteira.</t>
+          <t>Rede de profissionais do Direito com oportunidades de servico EM TODO O BRASIL. Site em manutencao, mas o formulario de contato esta ativo - deixe nome, e-mail, WhatsApp e mensagem.</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1918,56 +1926,56 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Habitamais Administradora de Condomínios</t>
+          <t>LS Correspondente Jurídico</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
+          <t>Manaus</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>contato@habtamais.com</t>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>contato@lscorrespondentejuridico.com.br</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Cobranca condominial judicial e extrajudicial</t>
+          <t>Cadastro no banco de correspondentes - parceria autonoma</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>https://habitamais.com21.com.br/</t>
+          <t>https://lscorrespondentejuridico.com.br/seja-nosso-parceiro/</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 3221-2063 | Rua Abuna, 1646, Olaria, Porto Velho/RO</t>
+          <t>Celular 92 98109-9962 | Rua 25, 982, Parque Dez de Novembro, Manaus/AM, CEP 69055-430</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>FORTE: o site tem servico declarado de GESTAO JURIDICA com "cobrancas judiciais e extrajudiciais". Atende quase 6.000 unidades residenciais. Demanda de cobranca em escala.</t>
+          <t>PAGINA "SEJA NOSSO PARCEIRO" com texto expresso: buscam alianca com advogados nao efetivos, em regime AUTONOMO e NAO EXCLUSIVO, encaminhando servicos de correspondente e clientes para trabalho conjunto. Regiao Norte.</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1976,56 +1984,56 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>JI-PARANÁ Contabilidade</t>
+          <t>Meu Correspondente Jurídico (Activeline)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>legalizacao@ji-paranacontabilidade.com.br</t>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>contato@activeline.com.br</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Parceria juridica e societario para a carteira</t>
+          <t>Cadastro gratuito como correspondente em RO</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>https://www.ji-paranacontabilidade.com.br/</t>
+          <t>https://meucorrespondentejuridico.com.br/</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 3422-1672 / (69) 99252-4880 | R. Joao Batista Neto, 1646, Nova Brasilia, Ji-Parana</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>NA SUA CIDADE. Assessora empresas na constituicao e encerramento - demanda societaria recorrente.</t>
+          <t>Cadastro TOTALMENTE GRATUITO, sem taxas. Abrangencia de comarcas definida por voce, ilimitada. Notificacoes de demanda por e-mail, telefone ou WhatsApp.</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2034,56 +2042,56 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="27" ht="62" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Lehmann Advogados</t>
+          <t>JurisConnect</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>adm@lehmann.adv.br</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>(11) 98201-4321</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Parceria entre escritorios e correspondencia</t>
+          <t>Cadastro como correspondente - sem mensalidade</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>https://lehmann.adv.br/advogados-ji-parana/</t>
+          <t>https://www.jurisconnect.com.br/</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Tel 81 3103-7007 | Seg-Sex 9h-18h</t>
+          <t>Tel e WhatsApp (11) 98201-4321 | JurisConnect Ltda</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Tem pagina TRABALHE CONOSCO. Atua em Ji-Parana, Vilhena e Rolim de Moura. Lista planos de saude, juros abusivos e dividas bancarias entre as areas.</t>
+          <t>CADASTRO GRATUITO, SEM MENSALIDADE - paga-se por demanda executada. Numeros do proprio site (14/09/2026): 3.044 demandas em 12 meses, 2.669 concluidas, 988 correspondentes com OAB. Tem pagina propria de cadastro de correspondente.</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2092,56 +2100,56 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="28" ht="62" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>OAB/RO - Seccional Rondônia</t>
+          <t>Nosso Direito - Diretório de Parceiros</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>gerencia@oab-ro.org.br</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>https://nossodireito.com/parceiros</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Convenios, credenciamentos e assistencia judiciaria</t>
+          <t>Cadastro gratuito no diretorio previdenciario nacional</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>https://www.oab-ro.org.br/</t>
+          <t>https://nossodireito.com/parceiros</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 3217-2100 / (69) 3217-2101 | Rua Paulo Leal, 1300, N. Sra. das Gracas, Porto Velho/RO | Outros e-mails publicados: presidencia@oab-ro.org.br, procuradoria@oab-ro.org.br, protocolo@oab-ro.org.br, ouvidoria@oab-ro.org.br, imprensa@oab-ro.org.br</t>
+          <t>Formulario pede: nome, OAB, email, WhatsApp, cidade, UF, area principal e volume mensal de casos</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>CANAL INSTITUCIONAL: a seccional divulga credenciamentos, convenios de assistencia judiciaria e editais. Vale perguntar pela lista de conveniados e pelo cadastro de dativos.</t>
+          <t>RENDA EXTRA DIRETA: cadastro GRATUITO, ABRANGENCIA NACIONAL, conecta REQUERENTES PREVIDENCIARIOS de todo o pais a advogados. Previdenciario e sua area principal. Faca hoje.</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2150,56 +2158,56 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="29" ht="62" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Reis &amp; Rocha Advogados Associados</t>
+          <t>Radar Gestão para Advogados - Banco de Talentos</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Cacoal</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>contato@reiserocha.com.br</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>https://radardagestao.com.br/vagas</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Parceria entre escritorios e correspondencia</t>
+          <t>Cadastro no banco de talentos - vagas remotas nacionais</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>https://reiserocha.com.br/</t>
+          <t>https://radardagestao.com.br/vagas</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 3441-2200 | R. Rui Barbosa, 1200, Centro, Cacoal-RO | OAB/RO 190000012-18</t>
+          <t>"Cadastre-se em nosso Banco de Talentos" | Recrutam para escritorios e departamentos juridicos em TODO O TERRITORIO NACIONAL, vagas presenciais E REMOTAS</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Areas batem com as suas: bancario, previdenciario, consumidor, tributario, trabalhista. Comarca vizinha.</t>
+          <t>Recrutadora especializada so em juridico. Cadastro no banco de talentos alimenta vagas remotas de todo o pais.</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2208,56 +2216,56 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="30" ht="62" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>RodaLog Logística</t>
+          <t>Brasil Correspondentes</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>atendimento@rodalog.com</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.brasilcorrespondentes.com.br/</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Assessoria juridica multi-comarca</t>
+          <t>Cadastro como correspondente</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>https://rodalog.com/</t>
+          <t>https://www.brasilcorrespondentes.com.br/</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>Tel (62) 3299-9974 | Matriz Goiania/GO</t>
+          <t>Planos a partir de R$ 14,98/mes</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>FILIAIS EM 10 COMARCAS DE RO: Vilhena, Pimenta Bueno, Cacoal, Presidente Medici, JI-PARANA, Ouro Preto do Oeste, Jaru, Ariquemes, Porto Velho, Guajara-Mirim. Passivo trabalhista e civel espalhado pelo estado.</t>
+          <t>Cadastro permite oferecer servicos em ate 3 cidades. Contato direto entre as partes, sem intermediario.</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2266,56 +2274,56 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="31" ht="62" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Rolim Net</t>
+          <t>Correspondente.com.br</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Rolim de Moura</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>contato@rolimnet.com.br</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>https://correspondente.com.br/</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Defesa em acoes consumeristas nas comarcas de RO</t>
+          <t>Cadastro como prestador na plataforma</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>https://www.rolimnet.com.br/</t>
+          <t>https://correspondente.com.br/</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>Av. Manaus, 5095, Centro, Rolim de Moura-RO | CNPJ 09.337.446/0001-80</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Provedor com 18 anos atendendo TODO o estado de RO e o Acre. Telecom e um dos setores mais acionados por consumidores (CNJ). Tem pagina Trabalhe Conosco.</t>
+          <t>Rede de mais de 20 mil prestadores. Fornece advogados para audiencias trabalhistas e civeis, presenciais e virtuais, alem de diligencias e protocolos.</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2324,56 +2332,56 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="32" ht="62" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>RondoCoop - Sistema OCB/RO</t>
+          <t>Correspondentes na Web</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>sistemaocb-ro@rondonia.coop.br</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>https://correspondentesnaweb.com.br/cadastro.html</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Convenio de assessoria juridica cooperativa</t>
+          <t>Cadastro gratuito como correspondente</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>https://rondonia.coop.br/rondocoop/</t>
+          <t>https://correspondentesnaweb.com.br/cadastro.html</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 99961-4247 / (69) 3224-6116 | R. Paulo Macalao, 4675, Porto Velho</t>
+          <t>CNPJ 19.770.735/0001-22</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Reune +20 cooperativas de RO. Tem pagina de Processos Seletivos e Licitacoes e Contratos.</t>
+          <t>CADASTRO BASICO GRATUITO. No formulario da para marcar os servicos: copias e protocolos, audiencias, e servicos em cartorios e prefeitura.</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2382,56 +2390,56 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="33" ht="62" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>UNICAFES Rondônia</t>
+          <t>GetNinjas</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>unicafes@unicafesro.org.br</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.getninjas.com.br/</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Assessoria previdenciaria rural e cooperativa</t>
+          <t>Cadastro como profissional (categoria Consultoria/Juridico)</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>https://unicafesro.org.br/quem-somos/</t>
+          <t>https://www.getninjas.com.br/</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 98462-7685 | Rua Missionaria Gunnar Vingren, 1448, Nova Brasilia, JI-PARANA/RO</t>
+          <t>Rua Dr. Fernandes Coelho, 85, 3o andar, Sao Paulo/SP | CNPJ 55.744.877/0001-89</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>SEDE NA SUA CIDADE. Uniao de cooperativas da agricultura familiar - publico direto de previdenciario rural.</t>
+          <t>Marketplace de servicos com area "Seja um profissional". Categoria Consultoria abrange servicos juridicos. Cliente vem por demanda.</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2440,56 +2448,56 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="34" ht="62" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Roque &amp; Lima Advocacia</t>
+          <t>Juris Correspondente</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Cacoal</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>WHATSAPP</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>(69) 98154-8887 / (69) 98428-1401</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.juriscorrespondente.com.br/seja-correspondente-juridico</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Parceria entre escritorios</t>
+          <t>Cadastro gratuito como correspondente</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>https://roqueelimaadvocacia.com.br/sobre/</t>
+          <t>https://www.juriscorrespondente.com.br/seja-correspondente-juridico</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>Rua Rio Branco, 2462, Centro, Cacoal/RO | Socios: Dr. Altemir Roque (OAB 1.311), Dra. Cristiane Rodrigues Lima (OAB/RO 7.220), Larissa H Roque (OAB/RO 13.210)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>ATENCAO: o e-mail do site e hi@example.com - placeholder de template, NAO usar. Contato real e o WhatsApp. Especialistas em Direito Medico e da Saude e Previdenciario - suas areas.</t>
+          <t>CADASTRO BASICO GRATUITO, planos pagos so ampliam visibilidade. Qualquer advogado com OAB pode se cadastrar.</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2498,56 +2506,56 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="35" ht="62" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Galvão &amp; Silva Advocacia</t>
+          <t>Jusbrasil - Diretório de Advogados</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
+          <t>Salvador</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>TELEFONE</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>0800 212 1700</t>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>https://www.jusbrasil.com.br/advogados</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia nas comarcas do interior de RO</t>
+          <t>Cadastro gratuito no diretorio nacional</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>https://www.galvaoesilva.com/escritorio-de-advocacia-em-porto-velho-ro/</t>
+          <t>https://www.jusbrasil.com.br/advogados</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>CNPJ 22.889.244/0001-00 | OAB/DF 2609/15</t>
+          <t>"E gratis e rapido se cadastrar"</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Banca nacional com unidade em Porto Velho. Tem pagina BANCO DE TALENTOS - caminho de entrada.</t>
+          <t>RENDA EXTRA: maior portal juridico do pais. Cadastro GRATUITO no diretorio gera contato direto de clientes. Depoimento no proprio site: advogada relata atender 99% dos casos sem reuniao presencial, so por telefone.</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2556,56 +2564,56 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="36" ht="62" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>MBT Advogados Associados</t>
+          <t>Migalhas Correspondentes</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>TELEFONE</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>+55 69 3421 3130</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>https://correspondentes.migalhas.com.br/</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Parceria entre escritorios</t>
+          <t>Cadastro como correspondente em RO</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>https://mbtadvocacia.com.br/</t>
+          <t>https://correspondentes.migalhas.com.br/</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Sede em Ji-Parana, filiais em Porto Velho e Vilhena</t>
+          <t>Planos: R$ 47/mes (4 meses) ate R$ 28,58/mes (24 meses)</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>NA SUA CIDADE. O site tem pagina VAGAS e pagina CONTATO - vale abrir. Areas: civil, trabalhista, ambiental, tributario, administrativo, cooperativo. Faz recuperacao judicial e falencias.</t>
+          <t>IMPORTANTE: tem secao "PRECISAMOS DE CORRESPONDENTES" listando as cidades com solicitacao de servico e SEM correspondente cadastrado. Vale checar se alguma comarca de RO esta nessa lista - entrada com demanda garantida.</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2614,56 +2622,56 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="37" ht="62" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Rede Hospitalar Samar</t>
+          <t>Via Justa (Justto)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>TELEFONE</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>0800 033 0393</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>https://www.justto.com.br/</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Contencioso de saude e trabalhista</t>
+          <t>Cadastro na area do advogado</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>https://hospitalsamar.com.br/</t>
+          <t>https://www.justto.com.br/</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>Unidades em Porto Velho, Cacoal e Ji-Parana</t>
+          <t>"Area do advogado: encontre oportunidades qualificadas compativeis com sua area de atuacao"</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>Maior rede hospitalar de RO. Tem pagina TRABALHE CONOSCO e pagina PARCEIROS.</t>
+          <t>Plataforma que recebe o problema do cidadao, faz a triagem e encaminha para advogado. Verifica OAB. Nao exige que o advogado seja da cidade do cliente - serve para atuacao remota.</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2672,56 +2680,56 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>2. RONDÔNIA — cliente ou parceiro local</t>
+    <row r="38" ht="62" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2. PLATAFORMA — cadastre-se e receba demanda</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Voo Transportes</t>
+          <t>Workana</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>TELEFONE</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>(69) 9908-1757</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>https://www.workana.com/pt</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Assessoria trabalhista e civel</t>
+          <t>Cadastro como freelancer juridico</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>https://www.vootransportes.com.br/</t>
+          <t>https://www.workana.com/pt</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Unidades: Ji-Parana (69) 9908-1757, Pimenta Bueno (69) 99226-5040, Porto Velho (69) 9983-0113, Rio Branco (68) 9232-9905, Guarulhos/SP (11) 2446-4276</t>
+          <t>Workana LLC | recebimento em moeda local OU EM DOLAR</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Unidade em Ji-Parana desde a fundacao. Sem e-mail no site.</t>
+          <t>RENDA EXTRA EM DOLAR: maior plataforma de freelance da America Latina. Projetos por objetivo ou por hora. Serve para elaboracao de pecas, pareceres e analise documental a distancia.</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2730,56 +2738,56 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
+    <row r="39" ht="62" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Bueno Brandão Advocacia</t>
+          <t>A Pioneira Administradora de Imóveis</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>contato@buenobrandao.adv.br</t>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>apioneira.adm@hotmail.com</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em saude nas comarcas de RO</t>
+          <t>Cobranca condominial, despejo, imobiliario</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>https://www.buenobrandao.adv.br/</t>
+          <t>http://apioneira.adm.br/</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>Tel (11) 3266-2067 | Alameda Casa Branca, 35, Cj. 510, Jd. Paulista, Sao Paulo/SP</t>
+          <t>Tel (69) 3221-5292 / (69) 99247-1837 | R. Mal. Deodoro, 2949, Olaria, Porto Velho | e-mail alternativo: admin@apioneira.adm.br</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>Especializada em Direito Medico e da Saude com atuacao em todo o territorio nacional.</t>
+          <t>Dois e-mails publicados no site. Gestao de condominios residenciais e comerciais.</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2788,56 +2796,56 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
+    <row r="40" ht="62" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CMP Prev Advocacia</t>
+          <t>André Ragnini Sociedade de Advogados</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Florianópolis</t>
+          <t>Cacoal</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>cmpprev@cmpprev.com.br</t>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>contato@andreragnini.com.br</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia previdenciaria em RO</t>
+          <t>Parceria entre escritorios e correspondencia</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>https://cmpprev.com.br/</t>
+          <t>https://andreragnini.com.br/</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>0800 025 5009 (Juridico) | (48) 3025-5008 | WhatsApp (48) 7602-0501 | R. Jeronimo Coelho, 170, sala 1001, Centro, Florianopolis/SC</t>
+          <t>Tel (69) 99960-1224 | Av. Belo Horizonte, 2.297, Cacoal/RO | Dr. Andre Bonifacio Queiroz Ragnini</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>ATENDE SEGURADOS DO INSS EM TODO O BRASIL, +25.000 casos. Escritorio oficial do SIMESC. Atuacao nacional sem estrutura local = precisam de correspondente para pericias e audiencias no JEF.</t>
+          <t>20+ anos em Cacoal. Atua em trabalhista, empresarial, tributario e previdenciario.</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2846,56 +2854,56 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
+    <row r="41" ht="62" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Campanella Advocacia</t>
+          <t>BRD Advocacia &amp; Advogados Associados</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>São Caetano do Sul</t>
+          <t>Ariquemes</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>contato@campanellaadvocacia.com.br</t>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Belnetobr@hotmail.com</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em saude nas comarcas de RO</t>
+          <t>Parceria entre escritorios e correspondencia</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>https://campanellaadvocacia.com.br/</t>
+          <t>https://www.brdadvocacia.com.br/</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>WhatsApp (11) 98118-0334 | Tel (11) 4224-3769 / 2988-7681 | Rua Para, 139, Sala 304, Centro, Sao Caetano do Sul-SP</t>
+          <t>Dr. Belmiro Rogerio Duarte Bermudes Neto | Tel (69) 98482-4171 | Av. Guapore, 2628, Setor 05, Ariquemes/RO</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>10+ anos em direito da saude: revisao de mensalidade por faixa etaria, home care, reembolso, erro medico e MEDICAMENTO DE ALTO CUSTO contra o SUS - exatamente o seu repertorio.</t>
+          <t>Ex-TJRO. Civel, previdenciario, trabalhista, criminal.</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2904,56 +2912,56 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42" ht="62" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Cardoso Advocacia</t>
+          <t>CDL Ji-Paraná - Câmara de Dirigentes Lojistas</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>contato@cardosoadvocacia.com.br</t>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>saa@cdljp-ro.com.br</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em saude nas comarcas de RO</t>
+          <t>Convenio de assessoria juridica para lojistas associados</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>https://cardosoadvocacia.com.br/</t>
+          <t>https://www.cdljipa.com.br/</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>Tel (71) 99695-0180 / (71) 3034-3159 | Sede Salvador/BA + unidade Pinheiros, Sao Paulo/SP | CNPJ 15.176.644/0001-02 | OAB/BA 2056/2011</t>
+          <t>Tel (69) 3421-9772 / 3422-3385 | Travessa da CDL, 221, Centro, Ji-Parana</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>Texto do site: "ATUAMOS NO BRASIL INTEIRO - estamos presentes em MAIS DE 21 ESTADOS". Planos de saude. Operacao nacional a distancia precisa de gente nas comarcas.</t>
+          <t>NA SUA CIDADE. Cobranca e consumidor sao demanda recorrente dos lojistas.</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2962,56 +2970,56 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
+    <row r="43" ht="62" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Delgado Azevedo Advogados</t>
+          <t>CF Contabilidade - Ji-Paraná</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Brasília</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>contato@delgadoazevedo.com.br</t>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>contato@cfjipa.com.br</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em saude nas comarcas de RO</t>
+          <t>Parceria juridica para a carteira de clientes PJ</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>https://www.delgadoazevedo.com.br/</t>
+          <t>https://cfcontabilidade.com.br/unidades/jipa/</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Tel (61) 99955-8009 | Gabriel Espindola de Souza OAB-DF 71.982</t>
+          <t>Contato: Viviane Melo L. Tavares | Tel (69) 99367-6377 | Rua Manoel Franco, 840, Ji-Parana</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Declaram ATUACAO NACIONAL e atendimento 24 horas, em todos os tribunais do Brasil. Liminar, home care, negativa de medicamento e internacao - teses que voce ja domina.</t>
+          <t>NA SUA CIDADE. Contabilidade desde 1989 - canal de indicacao de clientes empresariais.</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -3020,56 +3028,56 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" ht="62" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>GAMAA - Advocacia de Bancos &amp; Empresas</t>
+          <t>Expresso Rodotec (W S Transportes)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Belo Horizonte</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>contato@gamaa.com.br</t>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>contato@expressorodotec.com.br</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Parceria e correspondencia em RO</t>
+          <t>Assessoria trabalhista, tributaria e civel</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>https://gamaa.com.br/</t>
+          <t>https://www.expressorodotec.com/</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>Tel (31) 3274-9120 | R. Sao Paulo, 1071, 10o andar, Bloco B, Centro, BH/MG | Gilberto Miranda (proprietario)</t>
+          <t>Tel (69) 9988-9359 | WhatsApp (69) 99952-8263 | Rua Jorubatuba, 6403, Aeroclube, Porto Velho-RO | CNPJ 15.186.966/0001-32</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>TEXTO DO PROPRIO SITE: "firmou parcerias com diversos escritorios de advogados do pais e POSSUI VARIOS CORRESPONDENTES no interior do estado de Minas Gerais". Ja usam o modelo. Clientes: Santander, Azul, BRF, Danone, Pernambucanas, Leroy Merlin. Tem pagina PARCEIROS.</t>
+          <t>TEM PAGINA "SEJA PARCEIRO" E "TRABALHE CONOSCO" - dois canais de entrada. Clientes: DHL, Avon, Bemol.</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -3078,56 +3086,56 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
+    <row r="45" ht="62" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Gantus Advogados Associados</t>
+          <t>FACER - Federação das Assoc. Comerciais e Empresariais de RO</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>contato@gantusadvogados.com.br</t>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>contato@facer.org.br</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia para a carteira de massa em RO</t>
+          <t>Convenio de assessoria juridica para associados</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>https://gantusadvogados.com.br/</t>
+          <t>https://facer.org.br/institucional/sobre</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Tel (11) 94924-8141 / (11) 3813-5211 | Alameda Joaquim Eugenio de Lima, 696, Jardins, Sao Paulo/SP | Filial em Brasilia/DF | Fundador: Guilherme Miguel Gantus</t>
+          <t>Tel (69) 3229-8957 | Av. Calama 3250, Embratel, Porto Velho/RO</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>Area declarada de CONTENCIOSO DE MASSA e atuacao em TODO O TERRITORIO NACIONAL com apenas duas sedes (SP e DF). Dependem de correspondente fora do eixo.</t>
+          <t>ALAVANCA MAXIMA: 31 associacoes comerciais, +7 mil empresas, 52 municipios de RO. Um convenio abre a base inteira.</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -3136,56 +3144,56 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
+    <row r="46" ht="62" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Gilmar Araujo da Costa Advocacia</t>
+          <t>Habitamais Administradora de Condomínios</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>gac.advogado89@gmail.com</t>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>contato@habtamais.com</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em RO - consumidor e bancario</t>
+          <t>Cobranca condominial judicial e extrajudicial</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>https://gilmararaujoadvocacia.com.br/</t>
+          <t>https://habitamais.com21.com.br/</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>Tel (92) 98441-1276 | R. Rio Tarauaca, 36, Nossa Sra. das Gracas, Manaus-AM | CNPJ 46.366.996/0001-54</t>
+          <t>Tel (69) 3221-2063 | Rua Abuna, 1646, Olaria, Porto Velho/RO</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>Atuacao declarada EM TODO O BRASIL em consumidor e bancario: cartao RMC, consignado nao solicitado, juros abusivos, negativacao indevida. Mesmas teses que voce domina. Regiao Norte.</t>
+          <t>FORTE: o site tem servico declarado de GESTAO JURIDICA com "cobrancas judiciais e extrajudiciais". Atende quase 6.000 unidades residenciais. Demanda de cobranca em escala.</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -3194,56 +3202,56 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
+    <row r="47" ht="62" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>LDCM Advogados</t>
+          <t>JI-PARANÁ Contabilidade</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>contato@ldcm.com.br</t>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>legalizacao@ji-paranacontabilidade.com.br</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia para carteiras de bancario, telecom e varejo</t>
+          <t>Parceria juridica e societario para a carteira</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>https://www.ldcm.com.br/</t>
+          <t>https://www.ji-paranacontabilidade.com.br/</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Tel RJ +55 21 3500-3990 | SP +55 11 4380-8626 | Av. Epitacio Pessoa, 1.274, Ipanema, RJ | Av. Brig. Faria Lima, 4.300, Vila Olimpia, SP | E-mail nominal publicado: bruno.barreto@ldcm.com.br</t>
+          <t>Tel (69) 3422-1672 / (69) 99252-4880 | R. Joao Batista Neto, 1646, Nova Brasilia, Ji-Parana</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Boutique de disputas com carteira declarada em bancario, telecomunicacoes e varejo - os tres setores de maior contencioso de massa. So duas pracas.</t>
+          <t>NA SUA CIDADE. Assessora empresas na constituicao e encerramento - demanda societaria recorrente.</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -3252,56 +3260,56 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
+    <row r="48" ht="62" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Marcelo Tostes Advogados - contato geral</t>
+          <t>Lehmann Advogados</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Belo Horizonte</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>contato@mtostes.com.br</t>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>adm@lehmann.adv.br</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em RO / candidatura</t>
+          <t>Parceria entre escritorios e correspondencia</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>https://mtostes.com.br/</t>
+          <t>https://lehmann.adv.br/advogados-ji-parana/</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>Unidades e telefones: SP (11) 4837-3400, BH (31) 4501-4100, Porto Alegre (51) 3103-4901, Vitoria (27) 3345-1999, Brasilia (61) 3225-4774, Rio de Janeiro, Florianopolis</t>
+          <t>Tel 81 3103-7007 | Seg-Sex 9h-18h</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>SEGUNDO E-MAIL da banca (o outro e recrutamento@mtostes.com.br). Area declarada "Contencioso Escala" e "Service, Backoffice &amp; Gestao de Dados". Nenhuma unidade no Norte.</t>
+          <t>Tem pagina TRABALHE CONOSCO. Atua em Ji-Parana, Vilhena e Rolim de Moura. Lista planos de saude, juros abusivos e dividas bancarias entre as areas.</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3310,56 +3318,56 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
+    <row r="49" ht="62" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Parra Advogados</t>
+          <t>MBT Advogados Associados</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>contato@parraadvogados.com.br</t>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>contato@mbtadvocacia.com.br</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em saude e securitario em RO</t>
+          <t>Parceria entre escritorios</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>https://www.parraadvogados.com.br/</t>
+          <t>https://mbtadvocacia.com.br/</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>Tel (11) 2092-8728 / (11) 94529-1615 | R. Nova Jerusalem, 740, sala 1, Chacara Santo Antonio, Sao Paulo/SP | OAB/SP 18.155</t>
+          <t>Tel 69 3421-3130 | Ji-Parana: Av. Ji-Parana, 688, Urupa, CEP 76900-192 | Porto Velho: Av. Carlos Gomes, 513, s-205, Caiari | Vilhena: Av. Barao do Rio Branco, 4174, s-01, Centro | 08h-18h</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>ENCAIXE PERFEITO: o site diz que prestam servico "com atendimento em TODO BRASIL, presencial ou virtual, MEDIANTE CONTRATACAO POR SERVICO ou assessoria mensal". E o modelo de correspondente descrito com outras palavras. Especialistas em liminares contra planos de saude - sua area.</t>
+          <t>NA SUA CIDADE, com filiais em Porto Velho e Vilhena. O site tem pagina VAGAS propria. Areas: civil, trabalhista, ambiental, tributario, administrativo e COOPERATIVO. Faz recuperacao judicial, falencias e leiloes.</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3368,56 +3376,56 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
+    <row r="50" ht="62" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>R. Barreto Advogados</t>
+          <t>OAB/RO - Seccional Rondônia</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>rbarreto@rbarreto.adv.br</t>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>gerencia@oab-ro.org.br</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia e audiencias em RO</t>
+          <t>Convenios, credenciamentos e assistencia judiciaria</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>https://www.rbarreto.adv.br/</t>
+          <t>https://www.oab-ro.org.br/</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Tel (11) 3044-2293 | Av. Nove de Julho, 4254, Jardim Paulista, Sao Paulo/SP</t>
+          <t>Tel (69) 3217-2100 / (69) 3217-2101 | Rua Paulo Leal, 1300, N. Sra. das Gracas, Porto Velho/RO | Outros e-mails publicados: presidencia@oab-ro.org.br, procuradoria@oab-ro.org.br, protocolo@oab-ro.org.br, ouvidoria@oab-ro.org.br, imprensa@oab-ro.org.br</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Numeros do proprio site: +22.000 acoes contrarias, +4.000 processos de recuperacao de credito, R$ 80 milhoes recuperados. ATENDEM TODO O BRASIL DE FORMA REMOTA - precisam de gente em campo nas comarcas.</t>
+          <t>CANAL INSTITUCIONAL: a seccional divulga credenciamentos, convenios de assistencia judiciaria e editais. Vale perguntar pela lista de conveniados e pelo cadastro de dativos.</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3426,56 +3434,56 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
+    <row r="51" ht="62" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Ribeiro &amp; Feitoza Advogados</t>
+          <t>Reis &amp; Rocha Advogados Associados</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Cacoal</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>contato@ribeiroefeitozaadvogados.com</t>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>contato@reiserocha.com.br</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>Parceria e correspondencia na regiao Norte</t>
+          <t>Parceria entre escritorios e correspondencia</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>https://ribeiroefeitozaadvogados.com.br/</t>
+          <t>https://reiserocha.com.br/</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>Tel +55 92 99147-9179 | Avenida Getulio Vargas, 1222, Centro, Manaus/AM</t>
+          <t>Tel (69) 3441-2200 | R. Rui Barbosa, 1200, Centro, Cacoal-RO | OAB/RO 190000012-18</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>12 anos, referencia no Amazonas. Atuam em consumidor, bancario, licitacoes e ESG. Regiao Norte - logistica e cultura processual iguais as de RO.</t>
+          <t>Areas batem com as suas: bancario, previdenciario, consumidor, tributario, trabalhista. Comarca vizinha.</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3484,56 +3492,56 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
+    <row r="52" ht="62" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>SSantos Advogados</t>
+          <t>RodaLog Logística</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>advocacia@ssantos.adv.br</t>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>atendimento@rodalog.com</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia previdenciaria em RO</t>
+          <t>Assessoria juridica multi-comarca</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>https://ssantos.adv.br/</t>
+          <t>https://rodalog.com/</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>(41) 3023-1498 principal | (41) 98850-9639 comercial | Rua Emiliano Perneta, 680, 5o andar, Centro, Curitiba-PR</t>
+          <t>Tel (62) 3299-9974 | Matriz Goiania/GO</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>Presenca fisica em 6 ESTADOS (PR, SP, ES, BA, SP-Santos) e parceiros estrategicos em outros. 23 anos em revisao de aposentadoria. Parceria com +10 associacoes de aposentados. Norte descoberto.</t>
+          <t>FILIAIS EM 10 COMARCAS DE RO: Vilhena, Pimenta Bueno, Cacoal, Presidente Medici, JI-PARANA, Ouro Preto do Oeste, Jaru, Ariquemes, Porto Velho, Guajara-Mirim. Passivo trabalhista e civel espalhado pelo estado.</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3542,56 +3550,56 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
+    <row r="53" ht="62" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Tomás de Souza Sociedade de Advocacia</t>
+          <t>Rolim Net</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Brasília</t>
+          <t>Rolim de Moura</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>tomasdesouzaadvogados@gmail.com</t>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>contato@rolimnet.com.br</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Entrar na rede de advogados associados</t>
+          <t>Defesa em acoes consumeristas nas comarcas de RO</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>https://tomasdesouzaadvogados.com.br/</t>
+          <t>https://www.rolimnet.com.br/</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Tel (61) 99221-1401 | Sede: SMPW Q22, Cj 01, Lote 07, Casa B, Park Way, Brasilia/DF | Unidade: Rua 122, 216, Setor Sul, Goiania/GO</t>
+          <t>Tel e WhatsApp (69) 3198-0000 | Av. Manaus, 5095, Centro, Rolim de Moura-RO | CNPJ 09.337.446/0001-80</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>TEXTO DO SITE: atuam "com o APOIO DE UMA REDE DE ADVOGADOS ASSOCIADOS". Ja operam no modelo. Atuacao em tribunais superiores e Justica Federal. So duas pracas.</t>
+          <t>Provedor com 18 anos atendendo TODO o estado de RO e o Acre. Telecom e um dos setores mais acionados por consumidores (CNJ). Tem pagina Trabalhe Conosco.</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3600,56 +3608,56 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
+    <row r="54" ht="62" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Trajano Neto &amp; Paciornik Advogados (TNP)</t>
+          <t>RondoCoop - Sistema OCB/RO</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>contato@tnp.adv.br</t>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>sistemaocb-ro@rondonia.coop.br</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia na rede de coligados - comarcas de RO</t>
+          <t>Convenio de assessoria juridica cooperativa</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>https://tnp.adv.br/novosite/gestao-do-contencioso-de-massa/</t>
+          <t>https://rondonia.coop.br/rondocoop/</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>0800 575 0011 | +55 41 3075-5020 | Euripedes Garcez do Nascimento, 549, Ahu, Curitiba/PR</t>
+          <t>Tel (69) 99961-4247 / (69) 3224-6116 | R. Paulo Macalao, 4675, Porto Velho</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>ALVO NUMERO 1 DE CORRESPONDENCIA: area declarada de GESTAO DO CONTENCIOSO DE MASSA operando com "REDE DE COLIGADOS EM TODO BRASIL". Unidades: Brasilia, Natal, Sao Luis, Guarapuava, Florianopolis, Sao Paulo, Fortaleza - NENHUMA NO NORTE. Rondonia e buraco na malha deles.</t>
+          <t>Reune +20 cooperativas de RO. Tem pagina de Processos Seletivos e Licitacoes e Contratos.</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3658,56 +3666,56 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
+    <row r="55" ht="62" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Ultreia Contábil</t>
+          <t>UNICAFES Rondônia</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Brasília</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>assessoria@ultreiacontabil.com.br</t>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>unicafes@unicafesro.org.br</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Parceria contabil-juridica</t>
+          <t>Assessoria previdenciaria rural e cooperativa</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>https://ultreiacontabil.com.br/</t>
+          <t>https://unicafesro.org.br/quem-somos/</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Tel (61) 99694-5756</t>
+          <t>Tel (69) 98462-7685 | Rua Missionaria Gunnar Vingren, 1448, Nova Brasilia, JI-PARANA/RO</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>ATENDE ADVOGADOS como especialidade declarada, e faz Planejamento e Recuperacao Tributaria - parceria natural na sua area tributaria.</t>
+          <t>SEDE NA SUA CIDADE. Uniao de cooperativas da agricultura familiar - publico direto de previdenciario rural.</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3716,114 +3724,118 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
+    <row r="56" ht="62" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Bocchi Advogados Associados</t>
+          <t>Mind Consultoria de Gente e Gestão</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Ribeirão Preto</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>TELEFONE</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>0800 000 3373</t>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>(69) 99220-5249 / (69) 99962-7827</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia previdenciaria em RO</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr"/>
+          <t>Advogado(a) Associado(a) - Trabalhista Patronal | Ambiental | Civil (PJ)</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>https://bocchiadvogados.com.br/</t>
+          <t>https://to.indeed.com/aadzhybh6yrx</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>Rua Amador Bueno, 800, Ribeirao Preto/SP</t>
+          <t>"Apos realizar sua candidatura pelo site da Solides, envie uma mensagem no WhatsApp: (69) 99220-5249 / (69) 99962-7827. Informar: seu nome + vaga para a qual se candidatou"</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>50+ anos em previdenciario, trabalhista e civel. Texto do site: "fornecemos servicos juridicos para clientes de TODO BRASIL E DO MUNDO". Uma sede so - dependem de apoio local.</t>
+          <t>NA SUA CIDADE. Contrato de associacao PJ, R$ 2.500 + bonificacoes. O anuncio diz que NAO buscam perfil de previdenciario - enfatize trabalhista patronal, ambiental e civel.</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="60" customHeight="1">
+          <t>Descricao completa da vaga no Indeed (get_job_details)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="62" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Escobar Advogados - Programa de Parcerias</t>
+          <t>Roque &amp; Lima Advocacia</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Goiânia</t>
+          <t>Cacoal</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>TELEFONE</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>(62) 3280-9271</t>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>(69) 98154-8887 / (69) 98428-1401</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Programa de parcerias previdenciario</t>
+          <t>Parceria entre escritorios</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>https://escobaradvogados.com/parcerias/</t>
+          <t>https://roqueelimaadvocacia.com.br/sobre/</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>Responsavel: Dra. Ana Lara | Parceiro recebe relatorios mensais e reunioes trimestrais</t>
+          <t>Rua Rio Branco, 2462, Centro, Cacoal/RO | Socios: Dr. Altemir Roque (OAB 1.311), Dra. Cristiane Rodrigues Lima (OAB/RO 7.220), Larissa H Roque (OAB/RO 13.210)</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>ATENCAO: 1a fase limitada a GOIAS, expansao nacional prevista para a 2a etapa. Vale registrar interesse agora para entrar na expansao. Foco em beneficios do INSS.</t>
+          <t>ATENCAO: o e-mail do site e hi@example.com - placeholder de template, NAO usar. Contato real e o WhatsApp. Especialistas em Direito Medico e da Saude e Previdenciario - suas areas.</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3832,56 +3844,56 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
+    <row r="58" ht="62" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Medina, Ribeiro &amp; Aguiar Advogados (MRA)</t>
+          <t>Covezi Iveco</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>TELEFONE</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>(92) 3242-0464</t>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>(69) 3198-1099</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia na regiao Norte</t>
+          <t>Assessoria em consumidor, contratos e cobranca</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>https://www.medinaeribeiro.com/</t>
+          <t>https://www.covezi.com.br/</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>Forum Business Center, Sala 1702, Av. Andre Araujo, 97, Adrianopolis, Manaus/AM</t>
+          <t>Central 0800 942 1300 | Filiais RO: PORTO VELHO e VILHENA, ambas (69) 3198-1099 | Matriz Ap. de Goiania/GO | Outras filiais: Anapolis, Itumbiara, Rio Verde, Mineiros, Luziania, Brasilia, Gurupi, Palmas, Araguaina, Marituba/PA</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Full service empresarial no Amazonas, consultivo e contencioso. Regiao Norte.</t>
+          <t>DUAS filiais em Rondonia. Tem pagina TRABALHE CONOSCO e FALE CONOSCO. Venda de caminhoes pesados gera contencioso de consumidor, vicio de produto e cobranca.</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3890,56 +3902,56 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
+    <row r="59" ht="62" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>RS Advocacia Previdenciária (Ribeiro e Silva)</t>
+          <t>Galvão &amp; Silva Advocacia</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>TELEFONE</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>(11) 4210-0217</t>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>0800 212 1700</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia previdenciaria em RO</t>
+          <t>Correspondencia nas comarcas do interior de RO</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>https://rsadvocaciaprevidenciaria.com.br/</t>
+          <t>https://www.galvaoesilva.com/escritorio-de-advocacia-em-porto-velho-ro/</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>Telefone e WhatsApp (11) 4210-0217 | Av. Paulista, 1.106, 16o andar, Sala 1 | Unidade Mooca: Rua Ipanema, 80 | CNPJ 55.065.755/0001-10</t>
+          <t>CNPJ 22.889.244/0001-00 | OAB/DF 2609/15</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Atuam desde 2012 so em previdenciario, com CONSULTA ONLINE PARA TODO O BRASIL. BPC/LOAS, incapacidade, pensao por morte e revisoes - demandas do JEF de Ji-Parana.</t>
+          <t>Banca nacional com unidade em Porto Velho. Tem pagina BANCO DE TALENTOS - caminho de entrada.</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3948,56 +3960,56 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
+    <row r="60" ht="62" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>SA Law Advogados</t>
+          <t>Rede Hospitalar Samar</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>TELEFONE</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>+55 (11) 3288-6060</t>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>0800 033 0393</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia e candidatura (pagina Careers)</t>
+          <t>Contencioso de saude e trabalhista</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>https://salaw.com.br/</t>
+          <t>https://hospitalsamar.com.br/</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>SP: Av. Brig. Faria Lima, 3311, 3o andar, (11) 3288-6060 | RJ: Av. Rio Branco, 151, 5o andar, (21) 3553-1707</t>
+          <t>0800 033 0393 | Porto Velho: Av. Calama, 2585, Liberdade | Cacoal: Av. Sao Paulo, 2326, Centro | JI-PARANA: R. Padre Adolfo Rhol, 1267, Casa Preta</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Tem pagina CAREERS. Area declarada de Strategic Litigation and Arbitration.</t>
+          <t>Maior rede hospitalar de RO. Tem pagina TRABALHE CONOSCO e pagina PARCEIROS.</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -4006,56 +4018,56 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
+    <row r="61" ht="62" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Select Saúde (Select Operadora)</t>
+          <t>Voo Transportes</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Goiânia</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>TELEFONE</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>0800 224 2808</t>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>(69) 9908-1757</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Contencioso de saude suplementar</t>
+          <t>Assessoria trabalhista e civel</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>https://selectoperadora.com.br/</t>
+          <t>https://www.vootransportes.com.br/</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>St. Oeste, Goiania-GO</t>
+          <t>Unidades: Ji-Parana (69) 9908-1757, Pimenta Bueno (69) 99226-5040, Porto Velho (69) 9983-0113, Rio Branco (68) 9232-9905, Guarulhos/SP (11) 2446-4276</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>TEM PAGINA "SEJA UM CREDENCIADO" E "SEJA NOSSO PARCEIRO" - canais formais de entrada. Opera em Porto Velho e Ji-Parana.</t>
+          <t>Unidade em Ji-Parana desde a fundacao. Sem e-mail no site.</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -4064,56 +4076,56 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
+    <row r="62" ht="62" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+          <t>3. RONDÔNIA — cliente ou parceiro local</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Zveiter Advogados</t>
+          <t>Supermercados Irmãos Gonçalves</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Jaru</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>TELEFONE</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>55 (21) 3380-1155</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>https://www.irmaosgoncalves.com.br/</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia para as carteiras de massa</t>
+          <t>Assessoria trabalhista e consumerista</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>https://zveiter.com.br/</t>
+          <t>https://www.irmaosgoncalves.com.br/</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>Av. Presidente Antonio Carlos, 51, 19o e 20o andares, Centro, Rio de Janeiro/RJ | Fundado em 1957</t>
+          <t>Paginas: Central de Atendimento, FALE CONOSCO e TRABALHE CONOSCO | Tem cartao proprio (IG Card)</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>67 anos. Atua em contencioso de massa, saude suplementar, recuperacao judicial e falencias. Conduz as RJs do Grupo Petropolis e Grupo Americanas - carteiras com credores no pais inteiro.</t>
+          <t>3a maior empresa de Rondonia por faturamento (R$ 7,2 bi). O IG Card e credito proprio, o que soma contencioso bancario e de cobranca ao trabalhista e consumerista do varejo.</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -4122,20 +4134,20 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+    <row r="63" ht="62" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>ABL Advogados (Aith, Badari e Luchin)</t>
+          <t>Bueno Brandão Advocacia</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Santo André</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -4143,35 +4155,35 @@
           <t>SP</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>https://abladvogados.com/</t>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>contato@buenobrandao.adv.br</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Parceria previdenciaria - pagina PARA ADVOGADOS</t>
+          <t>Correspondencia em saude nas comarcas de RO</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>https://abladvogados.com/</t>
+          <t>https://www.buenobrandao.adv.br/</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Matriz Santo Andre/SP (11) 4509-4697 | filiais: Piracaia, Extrema/MG, Rio Claro 0800 707 4697, Mogi Mirim, Santos, Atibaia, Assis, Estiva Gerbi</t>
+          <t>Tel (11) 3266-2067 | Alameda Casa Branca, 35, Cj. 510, Jd. Paulista, Sao Paulo/SP</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>TEM MENU "PARA ADVOGADOS" E "TRABALHE CONOSCO" - canal especifico para parceria entre advogados. +90 profissionais so em previdenciario. Todas as filiais no Sudeste - Norte descoberto.</t>
+          <t>Especializada em Direito Medico e da Saude com atuacao em todo o territorio nacional.</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -4180,35 +4192,35 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+    <row r="64" ht="62" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Koetz Advocacia</t>
+          <t>CMP Prev Advocacia</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Porto Alegre</t>
+          <t>Florianópolis</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>https://koetzadvocacia.com.br/</t>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>cmpprev@cmpprev.com.br</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -4219,17 +4231,17 @@
       <c r="H64" s="4" t="inlineStr"/>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>https://koetzadvocacia.com.br/</t>
+          <t>https://cmpprev.com.br/</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>Contato pelo site | Eduardo Koetz (fundador), Murilo Mella (CEO)</t>
+          <t>0800 025 5009 (Juridico) | (48) 3025-5008 | WhatsApp (48) 7602-0501 | R. Jeronimo Coelho, 170, sala 1001, Centro, Florianopolis/SC</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>"Atendemos ONLINE qualquer pessoa em QUALQUER LUGAR DO MUNDO". Aposentadoria complexa e internacional. Operacao 100% digital precisa de presenca fisica para pericia e audiencia no JEF.</t>
+          <t>ATENDE SEGURADOS DO INSS EM TODO O BRASIL, +25.000 casos. Escritorio oficial do SIMESC. Atuacao nacional sem estrutura local = precisam de correspondente para pericias e audiencias no JEF.</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -4238,56 +4250,56 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+    <row r="65" ht="62" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Parish &amp; Zenandro Advogados</t>
+          <t>Campanella Advocacia</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>São Caetano do Sul</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>https://pz.adv.br/</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>contato@campanellaadvocacia.com.br</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia previdenciaria e do servidor</t>
+          <t>Correspondencia em saude nas comarcas de RO</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>https://pz.adv.br/</t>
+          <t>https://campanellaadvocacia.com.br/</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Matriz Salvador: Rua Frederico Simoes, 153, 13o andar, Caminho das Arvores | Unidades: Serrinha, Monte Gordo/Camacari, Retirolandia, Sao Goncalo dos Campos, Santaluz, Camacari, Feira de Santana</t>
+          <t>WhatsApp (11) 98118-0334 | Tel (11) 4224-3769 / 2988-7681 | Rua Para, 139, Sala 304, Centro, Sao Caetano do Sul-SP</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>88 PROFISSIONAIS na equipe juridica, todos concentrados na Bahia. Previdenciario, consumidor e trabalhista. Expansao para fora do estado exigiria parceiro local.</t>
+          <t>10+ anos em direito da saude: revisao de mensalidade por faixa etaria, home care, reembolso, erro medico e MEDICAMENTO DE ALTO CUSTO contra o SUS - exatamente o seu repertorio.</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -4296,56 +4308,56 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+    <row r="66" ht="62" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Vitorino &amp; Murta Advogados</t>
+          <t>Cardoso Advocacia</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Salvador</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>https://vitorinoemurta.com.br/</t>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>contato@cardosoadvocacia.com.br</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia bancaria em RO</t>
+          <t>Correspondencia em saude nas comarcas de RO</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>https://vitorinoemurta.com.br/escritorio-em-manaus/</t>
+          <t>https://cardosoadvocacia.com.br/</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>Contato por WhatsApp pelo site | Escritorios em Manaus, Sao Paulo, Brasilia, Florianopolis e Vila Velha</t>
+          <t>Tel (71) 99695-0180 / (71) 3034-3159 | Sede Salvador/BA + unidade Pinheiros, Sao Paulo/SP | CNPJ 15.176.644/0001-02 | OAB/BA 2056/2011</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>Maior banca de direito bancario do Norte. Atua em gestao de passivos bancarios e tributarios e execucao fiscal. Cinco pracas, nenhuma em RO.</t>
+          <t>Texto do site: "ATUAMOS NO BRASIL INTEIRO - estamos presentes em MAIS DE 21 ESTADOS". Planos de saude. Operacao nacional a distancia precisa de gente nas comarcas.</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -4354,56 +4366,56 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>3. BANCA NACIONAL — ofereça correspondência em RO</t>
+    <row r="67" ht="62" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Jurídico Certo</t>
+          <t>Delgado Azevedo Advogados</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Brasília</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>https://www.juridicocerto.com/cadastro-advogados-correspondentes-juridicos</t>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>contato@delgadoazevedo.com.br</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Cadastro como correspondente</t>
+          <t>Correspondencia em saude nas comarcas de RO</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>https://www.juridicocerto.com/cadastro-advogados-correspondentes-juridicos</t>
+          <t>https://www.delgadoazevedo.com.br/</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Plano Premium a partir de R$ 49/mes (anual). Cadastro inicial pede nome, e-mail profissional e senha</t>
+          <t>Tel (61) 99955-8009 | Gabriel Espindola de Souza OAB-DF 71.982</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>Tem o "Juridico Pag", que garante previsibilidade de recebimento. Algoritmo encaminha demandas proximas da sua localizacao. App avisa nova demanda.</t>
+          <t>Declaram ATUACAO NACIONAL e atendimento 24 horas, em todos os tribunais do Brasil. Liminar, home care, negativa de medicamento e internacao - teses que voce ja domina.</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4412,15 +4424,15 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
+    <row r="68" ht="62" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>4. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Juridigital (Drive Digital)</t>
+          <t>GAMAA - Advocacia de Bancos &amp; Empresas</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -4433,35 +4445,35 @@
           <t>MG</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>relacionamento@juridigital.com.br</t>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>contato@gamaa.com.br</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>Rede de BPO juridico e correspondencia</t>
+          <t>Parceria e correspondencia em RO</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>https://www.juridigital.com.br/bpo-juridico/</t>
+          <t>https://gamaa.com.br/</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>WhatsApp (31) 99362-8269 | Belo Horizonte/MG | CNPJ 28.407.867/0001-85</t>
+          <t>Tel (31) 3274-9120 | R. Sao Paulo, 1071, 10o andar, Bloco B, Centro, BH/MG | Gilberto Miranda (proprietario)</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>Produzem conteudo sobre BPO juridico E sobre contratacao de correspondente juridico - conhecem e intermediam os dois mercados. Base de escritorios clientes.</t>
+          <t>TEXTO DO PROPRIO SITE: "firmou parcerias com diversos escritorios de advogados do pais e POSSUI VARIOS CORRESPONDENTES no interior do estado de Minas Gerais". Ja usam o modelo. Clientes: Santander, Azul, BRF, Danone, Pernambucanas, Leroy Merlin. Tem pagina PARCEIROS.</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4470,56 +4482,56 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
+    <row r="69" ht="62" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>4. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>CSilva Sociedade de Advogados (BPO.CS)</t>
+          <t>Gantus Advogados Associados</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>https://csilvaadv.com.br/terceirizacao-de-servicos-juridicos/</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>contato@gantusadvogados.com.br</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Prestacao de servico para a operacao de BPO</t>
+          <t>Correspondencia para a carteira de massa em RO</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>https://csilvaadv.com.br/terceirizacao-de-servicos-juridicos/</t>
+          <t>https://gantusadvogados.com.br/</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Contato via WhatsApp pelo site</t>
+          <t>Tel (11) 94924-8141 / (11) 3813-5211 | Alameda Joaquim Eugenio de Lima, 696, Jardins, Sao Paulo/SP | Filial em Brasilia/DF | Fundador: Guilherme Miguel Gantus</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>Escritorio especializado em BPO Juridico para empresas de todos os portes.</t>
+          <t>Area declarada de CONTENCIOSO DE MASSA e atuacao em TODO O TERRITORIO NACIONAL com apenas duas sedes (SP e DF). Dependem de correspondente fora do eixo.</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4528,56 +4540,56 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
+    <row r="70" ht="62" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>4. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Carbonera &amp; Tomazini Advogados</t>
+          <t>Gilmar Araujo da Costa Advocacia</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Gravataí</t>
+          <t>Manaus</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>https://www.carboneraetomazini.com.br/</t>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>gac.advogado89@gmail.com</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>PARCERIA EM DIREITO PREVIDENCIARIO (pagina propria)</t>
+          <t>Correspondencia em RO - consumidor e bancario</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>https://www.carboneraetomazini.com.br/</t>
+          <t>https://gilmararaujoadvocacia.com.br/</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>Matriz Gravatai/RS (51) 3933-6733 | Filiais: Joinville (47) 3028-8555 e (47) 3017-5941, Rio Grande (53) 3035-3615, Fortaleza (85) 3032-4886 e (85) 3122-3878 | Escritorio Digital: (51) 3424-3615, (51) 99726-5382, (51) 99667-0941, (51) 99881-3738, (85) 98823-8227, (47) 98924-3140, (53) 99130-4900 | CNPJ 20.920.282/0001-52</t>
+          <t>Tel (92) 98441-1276 | R. Rio Tarauaca, 36, Nossa Sra. das Gracas, Manaus-AM | CNPJ 46.366.996/0001-54</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>MELHOR ACHADO DA RODADA: o menu do site tem item proprio "PARCERIA EM DIREITO PREVIDENCIARIO" e tambem "Trabalhe Conosco". Atendem todo o Brasil pelo Escritorio Digital. OAB/RS 5.067 e OAB/SC 4.029. Previdenciario e sua area principal.</t>
+          <t>Atuacao declarada EM TODO O BRASIL em consumidor e bancario: cartao RMC, consignado nao solicitado, juros abusivos, negativacao indevida. Mesmas teses que voce domina. Regiao Norte.</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4586,56 +4598,56 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
+    <row r="71" ht="62" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>4. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Ehts Consulting</t>
+          <t>LDCM Advogados</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>https://ehts.com.br/quem-somos/</t>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>contato@ldcm.com.br</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Prestacao de servico em legal operations</t>
+          <t>Correspondencia para carteiras de bancario, telecom e varejo</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>https://ehts.com.br/quem-somos/</t>
+          <t>https://www.ldcm.com.br/</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Contato pelo site e WhatsApp</t>
+          <t>Tel RJ +55 21 3500-3990 | SP +55 11 4380-8626 | Av. Epitacio Pessoa, 1.274, Ipanema, RJ | Av. Brig. Faria Lima, 4.300, Vila Olimpia, SP | E-mail nominal publicado: bruno.barreto@ldcm.com.br</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>Top 10 LegalTech do Brasil (Ranking 100 Open Startups). Clientes: Petrobras, Porto Seguro, Eurofarma, Renner, Centauro, Nike, Airbnb. Legal Operations e Analytics Juridico - carteiras enormes que precisam de maos.</t>
+          <t>Boutique de disputas com carteira declarada em bancario, telecomunicacoes e varejo - os tres setores de maior contencioso de massa. So duas pracas.</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4644,56 +4656,56 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
+    <row r="72" ht="62" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>4. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Intelligenti Stefanini - Locação de Headcounts</t>
+          <t>Marcelo Tostes Advogados - contato geral</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>https://www.intelligenti.com.br/solucoes/bpo-juridico</t>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>contato@mtostes.com.br</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>Alocacao como profissional juridico (headcount)</t>
+          <t>Correspondencia em RO / candidatura</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>https://www.intelligenti.com.br/solucoes/bpo-juridico</t>
+          <t>https://mtostes.com.br/</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>Av. Eusebio Matoso, 1375, Sao Paulo/SP | Grupo Stefanini</t>
+          <t>Unidades e telefones: SP (11) 4837-3400, BH (31) 4501-4100, Porto Alegre (51) 3103-4901, Vitoria (27) 3345-1999, Brasilia (61) 3225-4774, Rio de Janeiro, Florianopolis</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>MODELO IDEAL PARA RENDA EXTRA: tem servico declarado de "LOCACAO DE HEADCOUNTS - acesso rapido e flexivel a profissionais qualificados do setor juridico". Eles alocam advogados sob demanda. Ofereca-se como headcount disponivel.</t>
+          <t>SEGUNDO E-MAIL da banca (o outro e recrutamento@mtostes.com.br). Area declarada "Contencioso Escala" e "Service, Backoffice &amp; Gestao de Dados". Nenhuma unidade no Norte.</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -4702,56 +4714,56 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
+    <row r="73" ht="62" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>4. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Lima &amp; Pegolo Advogados (LPADV)</t>
+          <t>Nelson Wilians Advogados (NWADV) - fundador</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>https://limaepegolo.com.br/seja-um-parceiro/</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>nelson@nwadv.com.br</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Parceria com plataforma e teses prontas</t>
+          <t>Correspondencia / associacao - maior banca do pais</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>https://limaepegolo.com.br/seja-um-parceiro/</t>
+          <t>https://www.nwadv.com.br/</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Formulario na pagina "Seja um Parceiro"</t>
+          <t>Tel SP (11) 3330-2299 | Unidades com telefone proprio em TODOS os estados, incluindo RONDONIA | Manaus (92) 3659-3954, Rio Branco (68) 3222-8576, Macapa (96) 3224-1169, Brasilia (61) 3106-2000</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>MODELO INTERESSANTE: voce capta o cliente, eles assumem o trabalho tecnico. Texto do site: "uma vez validada a nova contratacao, TODO O TRABALHO SERA NOSSO". Da acesso a area restrita com teses do escritorio. Renda sem carga processual.</t>
+          <t>E-MAIL DO PROPRIO FUNDADOR publicado no site. Declaram PRESENCA FISICA EM TODOS OS ESTADOS BRASILEIROS. Ja tem unidade em Porto Velho - o encaixe aqui e cobrir as comarcas do INTERIOR de RO, onde a unidade da capital nao chega.</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -4760,562 +4772,2240 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
+    <row r="74" ht="62" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>4. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Souza Cruz Advogados - BPO Jurídico</t>
+          <t>Parra Advogados</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>https://souzacruz.adv.br/bpo-juridico/</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>contato@parraadvogados.com.br</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Prestacao de servico para a operacao de BPO trabalhista</t>
+          <t>Correspondencia em saude e securitario em RO</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
       <c r="I74" s="4" t="inlineStr">
         <is>
+          <t>https://www.parraadvogados.com.br/</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>Tel (11) 2092-8728 / (11) 94529-1615 | R. Nova Jerusalem, 740, sala 1, Chacara Santo Antonio, Sao Paulo/SP | OAB/SP 18.155</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>ENCAIXE PERFEITO: o site diz que prestam servico "com atendimento em TODO BRASIL, presencial ou virtual, MEDIANTE CONTRATACAO POR SERVICO ou assessoria mensal". E o modelo de correspondente descrito com outras palavras. Especialistas em liminares contra planos de saude - sua area.</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="62" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>R. Barreto Advogados</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>rbarreto@rbarreto.adv.br</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>Correspondencia e audiencias em RO</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rbarreto.adv.br/</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>Tel (11) 3044-2293 | Av. Nove de Julho, 4254, Jardim Paulista, Sao Paulo/SP</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Numeros do proprio site: +22.000 acoes contrarias, +4.000 processos de recuperacao de credito, R$ 80 milhoes recuperados. ATENDEM TODO O BRASIL DE FORMA REMOTA - precisam de gente em campo nas comarcas.</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="62" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Ribeiro &amp; Feitoza Advogados</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>contato@ribeiroefeitozaadvogados.com</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Parceria e correspondencia na regiao Norte</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>https://ribeiroefeitozaadvogados.com.br/</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>Tel +55 92 99147-9179 | Avenida Getulio Vargas, 1222, Centro, Manaus/AM</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>12 anos, referencia no Amazonas. Atuam em consumidor, bancario, licitacoes e ESG. Regiao Norte - logistica e cultura processual iguais as de RO.</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="62" customHeight="1">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>SSantos Advogados</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>advocacia@ssantos.adv.br</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>Correspondencia previdenciaria em RO</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>https://ssantos.adv.br/</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>(41) 3023-1498 principal | (41) 98850-9639 comercial | Rua Emiliano Perneta, 680, 5o andar, Centro, Curitiba-PR</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>Presenca fisica em 6 ESTADOS (PR, SP, ES, BA, SP-Santos) e parceiros estrategicos em outros. 23 anos em revisao de aposentadoria. Parceria com +10 associacoes de aposentados. Norte descoberto.</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="62" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Tomás de Souza Sociedade de Advocacia</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>tomasdesouzaadvogados@gmail.com</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Entrar na rede de advogados associados</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>https://tomasdesouzaadvogados.com.br/</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>Tel (61) 99221-1401 | Sede: SMPW Q22, Cj 01, Lote 07, Casa B, Park Way, Brasilia/DF | Unidade: Rua 122, 216, Setor Sul, Goiania/GO</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>TEXTO DO SITE: atuam "com o APOIO DE UMA REDE DE ADVOGADOS ASSOCIADOS". Ja operam no modelo. Atuacao em tribunais superiores e Justica Federal. So duas pracas.</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="62" customHeight="1">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Trajano Neto &amp; Paciornik Advogados (TNP)</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>contato@tnp.adv.br</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>Correspondencia na rede de coligados - comarcas de RO</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>https://tnp.adv.br/novosite/gestao-do-contencioso-de-massa/</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>0800 575 0011 | +55 41 3075-5020 | Euripedes Garcez do Nascimento, 549, Ahu, Curitiba/PR</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>ALVO NUMERO 1 DE CORRESPONDENCIA: area declarada de GESTAO DO CONTENCIOSO DE MASSA operando com "REDE DE COLIGADOS EM TODO BRASIL". Unidades: Brasilia, Natal, Sao Luis, Guarapuava, Florianopolis, Sao Paulo, Fortaleza - NENHUMA NO NORTE. Rondonia e buraco na malha deles.</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="62" customHeight="1">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Ultreia Contábil</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>assessoria@ultreiacontabil.com.br</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Parceria contabil-juridica</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>https://ultreiacontabil.com.br/</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>Tel (61) 99694-5756</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>ATENDE ADVOGADOS como especialidade declarada, e faz Planejamento e Recuperacao Tributaria - parceria natural na sua area tributaria.</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="62" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Amil</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>0800 721 1094</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Contencioso de saude suplementar</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amil.com.br/</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>Ouvidoria: 3004-1094 (capitais) e 0800 721 1094 (demais localidades) | Av. Dr. Chucri Zaidan, 1649, Ed. EZ Towers, Torre B, 23o andar, Sao Paulo/SP</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>Operadora que mais cresceu em marco de 2026. Carteira nacional com contencioso disperso.</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="62" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Bocchi Advogados Associados</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Ribeirão Preto</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>0800 000 3373</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Correspondencia previdenciaria em RO</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>https://bocchiadvogados.com.br/</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>Rua Amador Bueno, 800, Ribeirao Preto/SP</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>50+ anos em previdenciario, trabalhista e civel. Texto do site: "fornecemos servicos juridicos para clientes de TODO BRASIL E DO MUNDO". Uma sede so - dependem de apoio local.</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="62" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Escobar Advogados - Programa de Parcerias</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>(62) 3280-9271</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Programa de parcerias previdenciario</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>https://escobaradvogados.com/parcerias/</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>Responsavel: Dra. Ana Lara | Parceiro recebe relatorios mensais e reunioes trimestrais</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>ATENCAO: 1a fase limitada a GOIAS, expansao nacional prevista para a 2a etapa. Vale registrar interesse agora para entrar na expansao. Foco em beneficios do INSS.</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="62" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Hapvida NotreDame Intermédica</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>0800 280 9130</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Contencioso de saude suplementar</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hapvida.com.br/</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>0800 280 9130 (Norte e Nordeste) | 0800 018 3456 (Sul, Sudeste e Centro-Oeste) | Av. Heraclito Graca, 406, Centro, Fortaleza/CE | CNPJ 44.649.812/0001-38 | Tem TRABALHE CONOSCO e CANAL DE DENUNCIAS</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>Lider nacional em saude suplementar (8,8 milhoes de usuarios). Repare que tem 0800 ESPECIFICO para Norte e Nordeste - a operacao no Norte e separada.</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="62" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Medina, Ribeiro &amp; Aguiar Advogados (MRA)</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>(92) 3242-0464</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>Correspondencia na regiao Norte</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr"/>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>https://www.medinaeribeiro.com/</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>Forum Business Center, Sala 1702, Av. Andre Araujo, 97, Adrianopolis, Manaus/AM</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>Full service empresarial no Amazonas, consultivo e contencioso. Regiao Norte.</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="62" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>RS Advocacia Previdenciária (Ribeiro e Silva)</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>(11) 4210-0217</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>Correspondencia previdenciaria em RO</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>https://rsadvocaciaprevidenciaria.com.br/</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>Telefone e WhatsApp (11) 4210-0217 | Av. Paulista, 1.106, 16o andar, Sala 1 | Unidade Mooca: Rua Ipanema, 80 | CNPJ 55.065.755/0001-10</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>Atuam desde 2012 so em previdenciario, com CONSULTA ONLINE PARA TODO O BRASIL. BPC/LOAS, incapacidade, pensao por morte e revisoes - demandas do JEF de Ji-Parana.</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="62" customHeight="1">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>SA Law Advogados</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>+55 (11) 3288-6060</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>Correspondencia e candidatura (pagina Careers)</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>https://salaw.com.br/</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>SP: Av. Brig. Faria Lima, 3311, 3o andar, (11) 3288-6060 | RJ: Av. Rio Branco, 151, 5o andar, (21) 3553-1707</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>Tem pagina CAREERS. Area declarada de Strategic Litigation and Arbitration.</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="62" customHeight="1">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Select Saúde (Select Operadora)</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>0800 224 2808</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Contencioso de saude suplementar</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>https://selectoperadora.com.br/</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>St. Oeste, Goiania-GO</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>TEM PAGINA "SEJA UM CREDENCIADO" E "SEJA NOSSO PARCEIRO" - canais formais de entrada. Opera em Porto Velho e Ji-Parana.</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="62" customHeight="1">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Zveiter Advogados</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>55 (21) 3380-1155</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>Correspondencia para as carteiras de massa</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>https://zveiter.com.br/</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>Av. Presidente Antonio Carlos, 51, 19o e 20o andares, Centro, Rio de Janeiro/RJ | Fundado em 1957</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>67 anos. Atua em contencioso de massa, saude suplementar, recuperacao judicial e falencias. Conduz as RJs do Grupo Petropolis e Grupo Americanas - carteiras com credores no pais inteiro.</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="62" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>ABL Advogados (Aith, Badari e Luchin)</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Santo André</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>https://abladvogados.com/</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Parceria previdenciaria - pagina PARA ADVOGADOS</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>https://abladvogados.com/</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>Matriz Santo Andre/SP (11) 4509-4697 | filiais: Piracaia, Extrema/MG, Rio Claro 0800 707 4697, Mogi Mirim, Santos, Atibaia, Assis, Estiva Gerbi</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>TEM MENU "PARA ADVOGADOS" E "TRABALHE CONOSCO" - canal especifico para parceria entre advogados. +90 profissionais so em previdenciario. Todas as filiais no Sudeste - Norte descoberto.</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="62" customHeight="1">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Brasdiesel (Concessionária Scania)</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>https://www.brasdiesel.com.br/</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>Assessoria em consumidor e contratos</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.brasdiesel.com.br/</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>Paginas: Fale Conosco, TRABALHE CONOSCO, Vagas Disponiveis e COMPLIANCE BRASDIESEL</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>ATENCAO: este dominio e da concessionaria Scania, pode nao ser a TRR BrasDiesel de Ji-Parana do ranking Econodata - confirmar antes de abordar. Tem canal de compliance e vagas.</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="62" customHeight="1">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Energisa (grupo)</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Cataguases</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>https://www.energisa.com.br/</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Defesa em acoes consumeristas nas comarcas de RO</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.energisa.com.br/</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional lista atuacao em RONDONIA entre os estados atendidos, com acoes em Porto Velho e JI-PARANA</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>Concessionaria de energia e um dos setores mais acionados por consumidores segundo o CNJ. Atuacao confirmada em Ji-Parana no proprio site.</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="62" customHeight="1">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>JBS</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>https://www.jbs.com.br/</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>Assessoria trabalhista e doencas ocupacionais</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jbs.com.br/</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>+158 mil colaboradores no Brasil | +130 fabricas | presenca em 17 estados | pagina CARREIRAS</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>CINCO plantas em Rondonia (Vilhena, Sao Miguel do Guapore, Rolim de Moura, Ariquemes e Porto Velho). 158 mil empregados = passivo trabalhista e de doenca ocupacional em escala. Sua especialidade declarada.</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="62" customHeight="1">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Koetz Advocacia</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>https://koetzadvocacia.com.br/</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Correspondencia previdenciaria em RO</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>https://koetzadvocacia.com.br/</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>Contato pelo site | Eduardo Koetz (fundador), Murilo Mella (CEO)</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>"Atendemos ONLINE qualquer pessoa em QUALQUER LUGAR DO MUNDO". Aposentadoria complexa e internacional. Operacao 100% digital precisa de presenca fisica para pericia e audiencia no JEF.</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="62" customHeight="1">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Parish &amp; Zenandro Advogados</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>https://pz.adv.br/</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Correspondencia previdenciaria e do servidor</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>https://pz.adv.br/</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>Matriz Salvador: Rua Frederico Simoes, 153, 13o andar, Caminho das Arvores | Unidades: Serrinha, Monte Gordo/Camacari, Retirolandia, Sao Goncalo dos Campos, Santaluz, Camacari, Feira de Santana</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>88 PROFISSIONAIS na equipe juridica, todos concentrados na Bahia. Previdenciario, consumidor e trabalhista. Expansao para fora do estado exigiria parceiro local.</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="62" customHeight="1">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Vitorino &amp; Murta Advogados</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>https://vitorinoemurta.com.br/</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Correspondencia bancaria em RO</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>https://vitorinoemurta.com.br/escritorio-em-manaus/</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>Contato por WhatsApp pelo site | Escritorios em Manaus, Sao Paulo, Brasilia, Florianopolis e Vila Velha</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>Maior banca de direito bancario do Norte. Atua em gestao de passivos bancarios e tributarios e execucao fiscal. Cinco pracas, nenhuma em RO.</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="62" customHeight="1">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Jurídico Certo</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>https://www.juridicocerto.com/cadastro-advogados-correspondentes-juridicos</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Cadastro como correspondente</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.juridicocerto.com/cadastro-advogados-correspondentes-juridicos</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>Plano Premium a partir de R$ 49/mes (anual). Cadastro inicial pede nome, e-mail profissional e senha</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>Tem o "Juridico Pag", que garante previsibilidade de recebimento. Algoritmo encaminha demandas proximas da sua localizacao. App avisa nova demanda.</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="62" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>5. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Juridigital (Drive Digital)</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>relacionamento@juridigital.com.br</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Rede de BPO juridico e correspondencia</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.juridigital.com.br/bpo-juridico/</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp (31) 99362-8269 | Belo Horizonte/MG | CNPJ 28.407.867/0001-85</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>Produzem conteudo sobre BPO juridico E sobre contratacao de correspondente juridico - conhecem e intermediam os dois mercados. Base de escritorios clientes.</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="62" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>5. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>CSilva Sociedade de Advogados (BPO.CS)</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>https://csilvaadv.com.br/terceirizacao-de-servicos-juridicos/</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Prestacao de servico para a operacao de BPO</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>https://csilvaadv.com.br/terceirizacao-de-servicos-juridicos/</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>Contato via WhatsApp pelo site</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>Escritorio especializado em BPO Juridico para empresas de todos os portes.</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="62" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>5. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Carbonera &amp; Tomazini Advogados</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Gravataí</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>https://www.carboneraetomazini.com.br/</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>PARCERIA EM DIREITO PREVIDENCIARIO (pagina propria)</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.carboneraetomazini.com.br/</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>Matriz Gravatai/RS (51) 3933-6733 | Filiais: Joinville (47) 3028-8555 e (47) 3017-5941, Rio Grande (53) 3035-3615, Fortaleza (85) 3032-4886 e (85) 3122-3878 | Escritorio Digital: (51) 3424-3615, (51) 99726-5382, (51) 99667-0941, (51) 99881-3738, (85) 98823-8227, (47) 98924-3140, (53) 99130-4900 | CNPJ 20.920.282/0001-52</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>MELHOR ACHADO DA RODADA: o menu do site tem item proprio "PARCERIA EM DIREITO PREVIDENCIARIO" e tambem "Trabalhe Conosco". Atendem todo o Brasil pelo Escritorio Digital. OAB/RS 5.067 e OAB/SC 4.029. Previdenciario e sua area principal.</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="62" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>5. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Ehts Consulting</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>https://ehts.com.br/quem-somos/</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>Prestacao de servico em legal operations</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>https://ehts.com.br/quem-somos/</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>Contato pelo site e WhatsApp</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>Top 10 LegalTech do Brasil (Ranking 100 Open Startups). Clientes: Petrobras, Porto Seguro, Eurofarma, Renner, Centauro, Nike, Airbnb. Legal Operations e Analytics Juridico - carteiras enormes que precisam de maos.</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="62" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>5. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Intelligenti Stefanini - Locação de Headcounts</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>https://www.intelligenti.com.br/solucoes/bpo-juridico</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>Alocacao como profissional juridico (headcount)</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.intelligenti.com.br/solucoes/bpo-juridico</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>Av. Eusebio Matoso, 1375, Sao Paulo/SP | Grupo Stefanini</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>MODELO IDEAL PARA RENDA EXTRA: tem servico declarado de "LOCACAO DE HEADCOUNTS - acesso rapido e flexivel a profissionais qualificados do setor juridico". Eles alocam advogados sob demanda. Ofereca-se como headcount disponivel.</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="62" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>5. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Lima &amp; Pegolo Advogados (LPADV)</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>https://limaepegolo.com.br/seja-um-parceiro/</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>Parceria com plataforma e teses prontas</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>https://limaepegolo.com.br/seja-um-parceiro/</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>Formulario na pagina "Seja um Parceiro"</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>MODELO INTERESSANTE: voce capta o cliente, eles assumem o trabalho tecnico. Texto do site: "uma vez validada a nova contratacao, TODO O TRABALHO SERA NOSSO". Da acesso a area restrita com teses do escritorio. Renda sem carga processual.</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="62" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>5. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Souza Cruz Advogados - BPO Jurídico</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
           <t>https://souzacruz.adv.br/bpo-juridico/</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>Prestacao de servico para a operacao de BPO trabalhista</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>https://souzacruz.adv.br/bpo-juridico/</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
         <is>
           <t>Contato pelo site com a Dra. Mariana Cruz</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="K104" s="4" t="inlineStr">
         <is>
           <t>BPO trabalhista que atende escritorios e departamentos juridicos: controladoria, gestao de prazos, acompanhamento processual, elaboracao de pecas e sustentacoes. Eles COMPRAM o servico que voce vende.</t>
         </is>
       </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>Site institucional (extracao Tavily)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>5. VAGA ABERTA — candidate-se</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>Site institucional (extracao Tavily)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="62" customHeight="1">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>6. VAGA ABERTA — candidate-se</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>Carlos Miro Advogados</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>Uberlândia</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E105" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <t>yasminsantos@carlosmiro.adv.br</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>Advogado Contencioso Massificado</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
+      <c r="H105" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="I105" s="4" t="inlineStr">
         <is>
           <t>https://to.indeed.com/aanzcqdqkn8x</t>
         </is>
       </c>
-      <c r="J75" s="4" t="inlineStr">
+      <c r="J105" s="4" t="inlineStr">
         <is>
           <t>"Interessados na oportunidade podem se cadastrar por aqui ou enviar o curriculo para o e-mail yasminsantos@carlosmiro.adv.br"</t>
         </is>
       </c>
-      <c r="K75" s="4" t="inlineStr">
+      <c r="K105" s="4" t="inlineStr">
         <is>
           <t>50 anos de mercado, bancario e empresarial. O anuncio diz que ja opera com CORRESPONDENTES em diversas localidades do pais - vale ofertar RO na mesma mensagem.</t>
         </is>
       </c>
-      <c r="L75" s="4" t="inlineStr">
+      <c r="L105" s="4" t="inlineStr">
         <is>
           <t>Descricao completa da vaga no Indeed (get_job_details)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>5. VAGA ABERTA — candidate-se</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
+    <row r="106" ht="62" customHeight="1">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>6. VAGA ABERTA — candidate-se</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>Carneiro &amp; Ramalho Consultoria (p/ NEST Construções)</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>Jaboatão dos Guararapes</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D106" s="4" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E106" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <t>consultoraselecaopb@gmail.com</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G106" s="4" t="inlineStr">
         <is>
           <t>Advogado(a) Associado(a)</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="H106" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="I106" s="4" t="inlineStr">
         <is>
           <t>https://to.indeed.com/aagvvpqgq4h9</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="J106" s="4" t="inlineStr">
         <is>
           <t>"Enviar o curriculo para o e-mail: consultoraselecaopb@gmail.com"</t>
         </is>
       </c>
-      <c r="K76" s="4" t="inlineStr">
+      <c r="K106" s="4" t="inlineStr">
         <is>
           <t>Civel, execucao e cobranca, audiencias.</t>
         </is>
       </c>
-      <c r="L76" s="4" t="inlineStr">
+      <c r="L106" s="4" t="inlineStr">
         <is>
           <t>Descricao completa da vaga no Indeed (get_job_details)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>5. VAGA ABERTA — candidate-se</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
+    <row r="107" ht="62" customHeight="1">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>6. VAGA ABERTA — candidate-se</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>Décio Freire Advogados</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>Teresina</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D107" s="4" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E107" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <t>christianedepaula@deciofreire.com.br</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="G107" s="4" t="inlineStr">
         <is>
           <t>Advogado(a) Civel PLENO - Unidade Teresina (PJ)</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr">
+      <c r="H107" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="I107" s="4" t="inlineStr">
         <is>
           <t>https://to.indeed.com/aasphhw2vxx4</t>
         </is>
       </c>
-      <c r="J77" s="4" t="inlineStr">
+      <c r="J107" s="4" t="inlineStr">
         <is>
           <t>"Os(as) interessados(as) deverao encaminhar o curriculo informando a pretensao de honorarios para o e-mail christianedepaula@deciofreire.com.br"</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr">
+      <c r="K107" s="4" t="inlineStr">
         <is>
           <t>Banca nacional com escritorios em SP, RJ, BH, Brasilia e Recife. Exige informar pretensao de honorarios. Contratacao PJ.</t>
         </is>
       </c>
-      <c r="L77" s="4" t="inlineStr">
+      <c r="L107" s="4" t="inlineStr">
         <is>
           <t>Descricao completa da vaga no Indeed (get_job_details)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>5. VAGA ABERTA — candidate-se</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
+    <row r="108" ht="62" customHeight="1">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>6. VAGA ABERTA — candidate-se</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>GWF Advogados e Associados</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>Ribeirão Preto</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D108" s="4" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <t>gestao@gwfadvocacia.com.br</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="G108" s="4" t="inlineStr">
         <is>
           <t>Advogado(a) Senior Lider - Direito Bancario</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="H108" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="I108" s="4" t="inlineStr">
         <is>
           <t>https://to.indeed.com/aa6ntjfd4f72</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr">
+      <c r="J108" s="4" t="inlineStr">
         <is>
           <t>"Interessados podem encaminhar o curriculo para: gestao@gwfadvocacia.com.br"</t>
         </is>
       </c>
-      <c r="K78" s="4" t="inlineStr">
+      <c r="K108" s="4" t="inlineStr">
         <is>
           <t>Bancario e contencioso civel. Faixa ate R$ 15.000.</t>
         </is>
       </c>
-      <c r="L78" s="4" t="inlineStr">
+      <c r="L108" s="4" t="inlineStr">
         <is>
           <t>Descricao completa da vaga no Indeed (get_job_details)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>5. VAGA ABERTA — candidate-se</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
+    <row r="109" ht="62" customHeight="1">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>6. VAGA ABERTA — candidate-se</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>Gonçalves Júnior Advocacia</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>Brasília</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <t>contato@goncalvesjunioradv.com</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G109" s="4" t="inlineStr">
         <is>
           <t>Advogado(a) Associado(a) - Civel/Tributario | ATUACAO INICIAL REMOTA</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="H109" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="I109" s="4" t="inlineStr">
         <is>
           <t>https://to.indeed.com/aaw8gpwjhqy7</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="J109" s="4" t="inlineStr">
         <is>
           <t>"Os interessados deverao enviar curriculo para: contato@goncalvesjunioradv.com - Assunto: Processo Seletivo - Advogado(a) Associado(a) - Civel/Tributario"</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr">
+      <c r="K109" s="4" t="inlineStr">
         <is>
           <t>ATENCAO: o prazo do anuncio era 10/09/2026. Mas o proprio texto diz que aprovados ficam em cadastro por ate 6 meses - vale enviar assim mesmo.</t>
         </is>
       </c>
-      <c r="L79" s="4" t="inlineStr">
+      <c r="L109" s="4" t="inlineStr">
         <is>
           <t>Descricao completa da vaga no Indeed (get_job_details)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t>5. VAGA ABERTA — candidate-se</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
+    <row r="110" ht="62" customHeight="1">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>6. VAGA ABERTA — candidate-se</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>Marcelo Tostes Advogados Associados</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>Belo Horizonte</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D110" s="4" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E110" s="5" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <t>recrutamento@mtostes.com.br</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="G110" s="4" t="inlineStr">
         <is>
           <t>Advogado Civel Junior / Pleno - Contencioso de Escala</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="H110" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="I110" s="4" t="inlineStr">
         <is>
           <t>https://to.indeed.com/aazhlrrjljqn</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J110" s="4" t="inlineStr">
         <is>
           <t>"Candidate-se ou envie seu curriculo para recrutamento@mtostes.com.br indicando no assunto Advogado Civel - BH"</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr">
+      <c r="K110" s="4" t="inlineStr">
         <is>
           <t>Banca nacional de contencioso de massa e recuperacao de credito. Colocar o assunto pedido.</t>
         </is>
       </c>
-      <c r="L80" s="4" t="inlineStr">
+      <c r="L110" s="4" t="inlineStr">
         <is>
           <t>Descricao completa da vaga no Indeed (get_job_details)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>5. VAGA ABERTA — candidate-se</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>Mind Consultoria de Gente e Gestão</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>Ji-Paraná</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>WHATSAPP</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>(69) 99220-5249 / (69) 99962-7827</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>Advogado(a) Associado(a) - Trabalhista Patronal | Ambiental | Civil (PJ)</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t>https://to.indeed.com/aadzhybh6yrx</t>
-        </is>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>"Apos realizar sua candidatura pelo site da Solides, envie uma mensagem no WhatsApp: (69) 99220-5249 / (69) 99962-7827. Informar: seu nome + vaga para a qual se candidatou"</t>
-        </is>
-      </c>
-      <c r="K81" s="4" t="inlineStr">
-        <is>
-          <t>NA SUA CIDADE. Contrato de associacao PJ, R$ 2.500 + bonificacoes. O anuncio diz que NAO buscam perfil de previdenciario - enfatize trabalhista patronal, ambiental e civel.</t>
-        </is>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
+    <row r="111" ht="62" customHeight="1">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>6. VAGA ABERTA — candidate-se</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Reis Advogados Associados</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Uberlândia</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>https://reisadvogados.vagas.solides.com.br/vaga/915401</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>Assistente de Controladoria Juridica (PJ)</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>https://to.indeed.com/aay7xrjqdxpw</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>"REALIZAR CANDIDATURA NO LINK: https://reisadvogados.vagas.solides.com.br/vaga/915401"</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>Candidatura so pelo link proprio, nao pelo Indeed.</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
         <is>
           <t>Descricao completa da vaga no Indeed (get_job_details)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>5. VAGA ABERTA — candidate-se</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>Reis Advogados Associados</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Uberlândia</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>https://reisadvogados.vagas.solides.com.br/vaga/915401</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>Assistente de Controladoria Juridica (PJ)</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="I82" s="4" t="inlineStr">
-        <is>
-          <t>https://to.indeed.com/aay7xrjqdxpw</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>"REALIZAR CANDIDATURA NO LINK: https://reisadvogados.vagas.solides.com.br/vaga/915401"</t>
-        </is>
-      </c>
-      <c r="K82" s="4" t="inlineStr">
-        <is>
-          <t>Candidatura so pelo link proprio, nao pelo Indeed.</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>Descricao completa da vaga no Indeed (get_job_details)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L82"/>
+  <autoFilter ref="A1:L111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/prospeccao_juridica/RENDA_EXTRA_CONTATOS.xlsx
+++ b/prospeccao_juridica/RENDA_EXTRA_CONTATOS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONTATOS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONTATOS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CONTATOS'!$A$1:$L$111</definedName>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MBT Advogados Associados</t>
+          <t>OAB/RO - Seccional Rondônia</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3346,28 +3346,28 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>contato@mbtadvocacia.com.br</t>
+          <t>gerencia@oab-ro.org.br</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Parceria entre escritorios</t>
+          <t>Convenios, credenciamentos e assistencia judiciaria</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>https://mbtadvocacia.com.br/</t>
+          <t>https://www.oab-ro.org.br/</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>Tel 69 3421-3130 | Ji-Parana: Av. Ji-Parana, 688, Urupa, CEP 76900-192 | Porto Velho: Av. Carlos Gomes, 513, s-205, Caiari | Vilhena: Av. Barao do Rio Branco, 4174, s-01, Centro | 08h-18h</t>
+          <t>Tel (69) 3217-2100 / (69) 3217-2101 | Rua Paulo Leal, 1300, N. Sra. das Gracas, Porto Velho/RO | Outros e-mails publicados: presidencia@oab-ro.org.br, procuradoria@oab-ro.org.br, protocolo@oab-ro.org.br, ouvidoria@oab-ro.org.br, imprensa@oab-ro.org.br</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>NA SUA CIDADE, com filiais em Porto Velho e Vilhena. O site tem pagina VAGAS propria. Areas: civil, trabalhista, ambiental, tributario, administrativo e COOPERATIVO. Faz recuperacao judicial, falencias e leiloes.</t>
+          <t>CANAL INSTITUCIONAL: a seccional divulga credenciamentos, convenios de assistencia judiciaria e editais. Vale perguntar pela lista de conveniados e pelo cadastro de dativos.</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>OAB/RO - Seccional Rondônia</t>
+          <t>Reis &amp; Rocha Advogados Associados</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
+          <t>Cacoal</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3404,28 +3404,28 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>gerencia@oab-ro.org.br</t>
+          <t>contato@reiserocha.com.br</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Convenios, credenciamentos e assistencia judiciaria</t>
+          <t>Parceria entre escritorios e correspondencia</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>https://www.oab-ro.org.br/</t>
+          <t>https://reiserocha.com.br/</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 3217-2100 / (69) 3217-2101 | Rua Paulo Leal, 1300, N. Sra. das Gracas, Porto Velho/RO | Outros e-mails publicados: presidencia@oab-ro.org.br, procuradoria@oab-ro.org.br, protocolo@oab-ro.org.br, ouvidoria@oab-ro.org.br, imprensa@oab-ro.org.br</t>
+          <t>Tel (69) 3441-2200 | R. Rui Barbosa, 1200, Centro, Cacoal-RO | OAB/RO 190000012-18</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>CANAL INSTITUCIONAL: a seccional divulga credenciamentos, convenios de assistencia judiciaria e editais. Vale perguntar pela lista de conveniados e pelo cadastro de dativos.</t>
+          <t>Areas batem com as suas: bancario, previdenciario, consumidor, tributario, trabalhista. Comarca vizinha.</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Reis &amp; Rocha Advogados Associados</t>
+          <t>RodaLog Logística</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Cacoal</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3462,28 +3462,28 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>contato@reiserocha.com.br</t>
+          <t>atendimento@rodalog.com</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>Parceria entre escritorios e correspondencia</t>
+          <t>Assessoria juridica multi-comarca</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>https://reiserocha.com.br/</t>
+          <t>https://rodalog.com/</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 3441-2200 | R. Rui Barbosa, 1200, Centro, Cacoal-RO | OAB/RO 190000012-18</t>
+          <t>Tel (62) 3299-9974 | Matriz Goiania/GO</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Areas batem com as suas: bancario, previdenciario, consumidor, tributario, trabalhista. Comarca vizinha.</t>
+          <t>FILIAIS EM 10 COMARCAS DE RO: Vilhena, Pimenta Bueno, Cacoal, Presidente Medici, JI-PARANA, Ouro Preto do Oeste, Jaru, Ariquemes, Porto Velho, Guajara-Mirim. Passivo trabalhista e civel espalhado pelo estado.</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>RodaLog Logística</t>
+          <t>Rolim Net</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>Rolim de Moura</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3520,28 +3520,28 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>atendimento@rodalog.com</t>
+          <t>contato@rolimnet.com.br</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>Assessoria juridica multi-comarca</t>
+          <t>Defesa em acoes consumeristas nas comarcas de RO</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>https://rodalog.com/</t>
+          <t>https://www.rolimnet.com.br/</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>Tel (62) 3299-9974 | Matriz Goiania/GO</t>
+          <t>Tel e WhatsApp (69) 3198-0000 | Av. Manaus, 5095, Centro, Rolim de Moura-RO | CNPJ 09.337.446/0001-80</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>FILIAIS EM 10 COMARCAS DE RO: Vilhena, Pimenta Bueno, Cacoal, Presidente Medici, JI-PARANA, Ouro Preto do Oeste, Jaru, Ariquemes, Porto Velho, Guajara-Mirim. Passivo trabalhista e civel espalhado pelo estado.</t>
+          <t>Provedor com 18 anos atendendo TODO o estado de RO e o Acre. Telecom e um dos setores mais acionados por consumidores (CNJ). Tem pagina Trabalhe Conosco.</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Rolim Net</t>
+          <t>RondoCoop - Sistema OCB/RO</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Rolim de Moura</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3578,28 +3578,28 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>contato@rolimnet.com.br</t>
+          <t>sistemaocb-ro@rondonia.coop.br</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Defesa em acoes consumeristas nas comarcas de RO</t>
+          <t>Convenio de assessoria juridica cooperativa</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>https://www.rolimnet.com.br/</t>
+          <t>https://rondonia.coop.br/rondocoop/</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Tel e WhatsApp (69) 3198-0000 | Av. Manaus, 5095, Centro, Rolim de Moura-RO | CNPJ 09.337.446/0001-80</t>
+          <t>Tel (69) 99961-4247 / (69) 3224-6116 | R. Paulo Macalao, 4675, Porto Velho</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Provedor com 18 anos atendendo TODO o estado de RO e o Acre. Telecom e um dos setores mais acionados por consumidores (CNJ). Tem pagina Trabalhe Conosco.</t>
+          <t>Reune +20 cooperativas de RO. Tem pagina de Processos Seletivos e Licitacoes e Contratos.</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>RondoCoop - Sistema OCB/RO</t>
+          <t>UNICAFES Rondônia</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3636,28 +3636,28 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>sistemaocb-ro@rondonia.coop.br</t>
+          <t>unicafes@unicafesro.org.br</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Convenio de assessoria juridica cooperativa</t>
+          <t>Assessoria previdenciaria rural e cooperativa</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>https://rondonia.coop.br/rondocoop/</t>
+          <t>https://unicafesro.org.br/quem-somos/</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 99961-4247 / (69) 3224-6116 | R. Paulo Macalao, 4675, Porto Velho</t>
+          <t>Tel (69) 98462-7685 | Rua Missionaria Gunnar Vingren, 1448, Nova Brasilia, JI-PARANA/RO</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Reune +20 cooperativas de RO. Tem pagina de Processos Seletivos e Licitacoes e Contratos.</t>
+          <t>SEDE NA SUA CIDADE. Uniao de cooperativas da agricultura familiar - publico direto de previdenciario rural.</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>UNICAFES Rondônia</t>
+          <t>Mind Consultoria de Gente e Gestão</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3687,40 +3687,44 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>WHATSAPP</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>unicafes@unicafesro.org.br</t>
+          <t>(69) 99220-5249 / (69) 99962-7827</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Assessoria previdenciaria rural e cooperativa</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr"/>
+          <t>Advogado(a) Associado(a) - Trabalhista Patronal | Ambiental | Civil (PJ)</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>https://unicafesro.org.br/quem-somos/</t>
+          <t>https://to.indeed.com/aadzhybh6yrx</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Tel (69) 98462-7685 | Rua Missionaria Gunnar Vingren, 1448, Nova Brasilia, JI-PARANA/RO</t>
+          <t>"Apos realizar sua candidatura pelo site da Solides, envie uma mensagem no WhatsApp: (69) 99220-5249 / (69) 99962-7827. Informar: seu nome + vaga para a qual se candidatou"</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>SEDE NA SUA CIDADE. Uniao de cooperativas da agricultura familiar - publico direto de previdenciario rural.</t>
+          <t>NA SUA CIDADE. Contrato de associacao PJ, R$ 2.500 + bonificacoes. O anuncio diz que NAO buscam perfil de previdenciario - enfatize trabalhista patronal, ambiental e civel.</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
+          <t>Descricao completa da vaga no Indeed (get_job_details)</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3736,12 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Mind Consultoria de Gente e Gestão</t>
+          <t>Roque &amp; Lima Advocacia</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>Cacoal</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3752,37 +3756,33 @@
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>(69) 99220-5249 / (69) 99962-7827</t>
+          <t>(69) 98154-8887 / (69) 98428-1401</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Advogado(a) Associado(a) - Trabalhista Patronal | Ambiental | Civil (PJ)</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
+          <t>Parceria entre escritorios</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr"/>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>https://to.indeed.com/aadzhybh6yrx</t>
+          <t>https://roqueelimaadvocacia.com.br/sobre/</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>"Apos realizar sua candidatura pelo site da Solides, envie uma mensagem no WhatsApp: (69) 99220-5249 / (69) 99962-7827. Informar: seu nome + vaga para a qual se candidatou"</t>
+          <t>Rua Rio Branco, 2462, Centro, Cacoal/RO | Socios: Dr. Altemir Roque (OAB 1.311), Dra. Cristiane Rodrigues Lima (OAB/RO 7.220), Larissa H Roque (OAB/RO 13.210)</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>NA SUA CIDADE. Contrato de associacao PJ, R$ 2.500 + bonificacoes. O anuncio diz que NAO buscam perfil de previdenciario - enfatize trabalhista patronal, ambiental e civel.</t>
+          <t>ATENCAO: o e-mail do site e hi@example.com - placeholder de template, NAO usar. Contato real e o WhatsApp. Especialistas em Direito Medico e da Saude e Previdenciario - suas areas.</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>Descricao completa da vaga no Indeed (get_job_details)</t>
+          <t>Site institucional (extracao Tavily)</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Roque &amp; Lima Advocacia</t>
+          <t>Covezi Iveco</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Cacoal</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3807,35 +3807,35 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>WHATSAPP</t>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>(69) 98154-8887 / (69) 98428-1401</t>
+          <t>(69) 3198-1099</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Parceria entre escritorios</t>
+          <t>Assessoria em consumidor, contratos e cobranca</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>https://roqueelimaadvocacia.com.br/sobre/</t>
+          <t>https://www.covezi.com.br/</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>Rua Rio Branco, 2462, Centro, Cacoal/RO | Socios: Dr. Altemir Roque (OAB 1.311), Dra. Cristiane Rodrigues Lima (OAB/RO 7.220), Larissa H Roque (OAB/RO 13.210)</t>
+          <t>Central 0800 942 1300 | Filiais RO: PORTO VELHO e VILHENA, ambas (69) 3198-1099 | Matriz Ap. de Goiania/GO | Outras filiais: Anapolis, Itumbiara, Rio Verde, Mineiros, Luziania, Brasilia, Gurupi, Palmas, Araguaina, Marituba/PA</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>ATENCAO: o e-mail do site e hi@example.com - placeholder de template, NAO usar. Contato real e o WhatsApp. Especialistas em Direito Medico e da Saude e Previdenciario - suas areas.</t>
+          <t>DUAS filiais em Rondonia. Tem pagina TRABALHE CONOSCO e FALE CONOSCO. Venda de caminhoes pesados gera contencioso de consumidor, vicio de produto e cobranca.</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Covezi Iveco</t>
+          <t>Galvão &amp; Silva Advocacia</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3872,28 +3872,28 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>(69) 3198-1099</t>
+          <t>0800 212 1700</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Assessoria em consumidor, contratos e cobranca</t>
+          <t>Correspondencia nas comarcas do interior de RO</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>https://www.covezi.com.br/</t>
+          <t>https://www.galvaoesilva.com/escritorio-de-advocacia-em-porto-velho-ro/</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>Central 0800 942 1300 | Filiais RO: PORTO VELHO e VILHENA, ambas (69) 3198-1099 | Matriz Ap. de Goiania/GO | Outras filiais: Anapolis, Itumbiara, Rio Verde, Mineiros, Luziania, Brasilia, Gurupi, Palmas, Araguaina, Marituba/PA</t>
+          <t>CNPJ 22.889.244/0001-00 | OAB/DF 2609/15</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>DUAS filiais em Rondonia. Tem pagina TRABALHE CONOSCO e FALE CONOSCO. Venda de caminhoes pesados gera contencioso de consumidor, vicio de produto e cobranca.</t>
+          <t>Banca nacional com unidade em Porto Velho. Tem pagina BANCO DE TALENTOS - caminho de entrada.</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Galvão &amp; Silva Advocacia</t>
+          <t>Rede Hospitalar Samar</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3930,28 +3930,28 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>0800 212 1700</t>
+          <t>0800 033 0393</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia nas comarcas do interior de RO</t>
+          <t>Contencioso de saude e trabalhista</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>https://www.galvaoesilva.com/escritorio-de-advocacia-em-porto-velho-ro/</t>
+          <t>https://hospitalsamar.com.br/</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>CNPJ 22.889.244/0001-00 | OAB/DF 2609/15</t>
+          <t>0800 033 0393 | Porto Velho: Av. Calama, 2585, Liberdade | Cacoal: Av. Sao Paulo, 2326, Centro | JI-PARANA: R. Padre Adolfo Rhol, 1267, Casa Preta</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Banca nacional com unidade em Porto Velho. Tem pagina BANCO DE TALENTOS - caminho de entrada.</t>
+          <t>Maior rede hospitalar de RO. Tem pagina TRABALHE CONOSCO e pagina PARCEIROS.</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Rede Hospitalar Samar</t>
+          <t>Voo Transportes</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Porto Velho</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3988,28 +3988,28 @@
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>0800 033 0393</t>
+          <t>(69) 9908-1757</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Contencioso de saude e trabalhista</t>
+          <t>Assessoria trabalhista e civel</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>https://hospitalsamar.com.br/</t>
+          <t>https://www.vootransportes.com.br/</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>0800 033 0393 | Porto Velho: Av. Calama, 2585, Liberdade | Cacoal: Av. Sao Paulo, 2326, Centro | JI-PARANA: R. Padre Adolfo Rhol, 1267, Casa Preta</t>
+          <t>Unidades: Ji-Parana (69) 9908-1757, Pimenta Bueno (69) 99226-5040, Porto Velho (69) 9983-0113, Rio Branco (68) 9232-9905, Guarulhos/SP (11) 2446-4276</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Maior rede hospitalar de RO. Tem pagina TRABALHE CONOSCO e pagina PARCEIROS.</t>
+          <t>Unidade em Ji-Parana desde a fundacao. Sem e-mail no site.</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Voo Transportes</t>
+          <t>Supermercados Irmãos Gonçalves</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>Jaru</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -4039,35 +4039,35 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>TELEFONE</t>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>(69) 9908-1757</t>
+          <t>https://www.irmaosgoncalves.com.br/</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Assessoria trabalhista e civel</t>
+          <t>Assessoria trabalhista e consumerista</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>https://www.vootransportes.com.br/</t>
+          <t>https://www.irmaosgoncalves.com.br/</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Unidades: Ji-Parana (69) 9908-1757, Pimenta Bueno (69) 99226-5040, Porto Velho (69) 9983-0113, Rio Branco (68) 9232-9905, Guarulhos/SP (11) 2446-4276</t>
+          <t>Paginas: Central de Atendimento, FALE CONOSCO e TRABALHE CONOSCO | Tem cartao proprio (IG Card)</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>Unidade em Ji-Parana desde a fundacao. Sem e-mail no site.</t>
+          <t>3a maior empresa de Rondonia por faturamento (R$ 7,2 bi). O IG Card e credito proprio, o que soma contencioso bancario e de cobranca ao trabalhista e consumerista do varejo.</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -4077,55 +4077,55 @@
       </c>
     </row>
     <row r="62" ht="62" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>3. RONDÔNIA — cliente ou parceiro local</t>
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Supermercados Irmãos Gonçalves</t>
+          <t>Bueno Brandão Advocacia</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Jaru</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>https://www.irmaosgoncalves.com.br/</t>
+          <t>contato@buenobrandao.adv.br</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>Assessoria trabalhista e consumerista</t>
+          <t>Correspondencia em saude nas comarcas de RO</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>https://www.irmaosgoncalves.com.br/</t>
+          <t>https://www.buenobrandao.adv.br/</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>Paginas: Central de Atendimento, FALE CONOSCO e TRABALHE CONOSCO | Tem cartao proprio (IG Card)</t>
+          <t>Tel (11) 3266-2067 | Alameda Casa Branca, 35, Cj. 510, Jd. Paulista, Sao Paulo/SP</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>3a maior empresa de Rondonia por faturamento (R$ 7,2 bi). O IG Card e credito proprio, o que soma contencioso bancario e de cobranca ao trabalhista e consumerista do varejo.</t>
+          <t>Especializada em Direito Medico e da Saude com atuacao em todo o territorio nacional.</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -4142,17 +4142,17 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Bueno Brandão Advocacia</t>
+          <t>CMP Prev Advocacia</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Florianópolis</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -4162,28 +4162,28 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>contato@buenobrandao.adv.br</t>
+          <t>cmpprev@cmpprev.com.br</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em saude nas comarcas de RO</t>
+          <t>Correspondencia previdenciaria em RO</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>https://www.buenobrandao.adv.br/</t>
+          <t>https://cmpprev.com.br/</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Tel (11) 3266-2067 | Alameda Casa Branca, 35, Cj. 510, Jd. Paulista, Sao Paulo/SP</t>
+          <t>0800 025 5009 (Juridico) | (48) 3025-5008 | WhatsApp (48) 7602-0501 | R. Jeronimo Coelho, 170, sala 1001, Centro, Florianopolis/SC</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>Especializada em Direito Medico e da Saude com atuacao em todo o territorio nacional.</t>
+          <t>ATENDE SEGURADOS DO INSS EM TODO O BRASIL, +25.000 casos. Escritorio oficial do SIMESC. Atuacao nacional sem estrutura local = precisam de correspondente para pericias e audiencias no JEF.</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -4200,17 +4200,17 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>CMP Prev Advocacia</t>
+          <t>Campanella Advocacia</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Florianópolis</t>
+          <t>São Caetano do Sul</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -4220,28 +4220,28 @@
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>cmpprev@cmpprev.com.br</t>
+          <t>contato@campanellaadvocacia.com.br</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia previdenciaria em RO</t>
+          <t>Correspondencia em saude nas comarcas de RO</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>https://cmpprev.com.br/</t>
+          <t>https://campanellaadvocacia.com.br/</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>0800 025 5009 (Juridico) | (48) 3025-5008 | WhatsApp (48) 7602-0501 | R. Jeronimo Coelho, 170, sala 1001, Centro, Florianopolis/SC</t>
+          <t>WhatsApp (11) 98118-0334 | Tel (11) 4224-3769 / 2988-7681 | Rua Para, 139, Sala 304, Centro, Sao Caetano do Sul-SP</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>ATENDE SEGURADOS DO INSS EM TODO O BRASIL, +25.000 casos. Escritorio oficial do SIMESC. Atuacao nacional sem estrutura local = precisam de correspondente para pericias e audiencias no JEF.</t>
+          <t>10+ anos em direito da saude: revisao de mensalidade por faixa etaria, home care, reembolso, erro medico e MEDICAMENTO DE ALTO CUSTO contra o SUS - exatamente o seu repertorio.</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -4258,17 +4258,17 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Campanella Advocacia</t>
+          <t>Cardoso Advocacia</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>São Caetano do Sul</t>
+          <t>Salvador</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>contato@campanellaadvocacia.com.br</t>
+          <t>contato@cardosoadvocacia.com.br</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -4289,17 +4289,17 @@
       <c r="H65" s="4" t="inlineStr"/>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>https://campanellaadvocacia.com.br/</t>
+          <t>https://cardosoadvocacia.com.br/</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>WhatsApp (11) 98118-0334 | Tel (11) 4224-3769 / 2988-7681 | Rua Para, 139, Sala 304, Centro, Sao Caetano do Sul-SP</t>
+          <t>Tel (71) 99695-0180 / (71) 3034-3159 | Sede Salvador/BA + unidade Pinheiros, Sao Paulo/SP | CNPJ 15.176.644/0001-02 | OAB/BA 2056/2011</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>10+ anos em direito da saude: revisao de mensalidade por faixa etaria, home care, reembolso, erro medico e MEDICAMENTO DE ALTO CUSTO contra o SUS - exatamente o seu repertorio.</t>
+          <t>Texto do site: "ATUAMOS NO BRASIL INTEIRO - estamos presentes em MAIS DE 21 ESTADOS". Planos de saude. Operacao nacional a distancia precisa de gente nas comarcas.</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Cardoso Advocacia</t>
+          <t>Delgado Azevedo Advogados</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>Brasília</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>contato@cardosoadvocacia.com.br</t>
+          <t>contato@delgadoazevedo.com.br</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -4347,17 +4347,17 @@
       <c r="H66" s="4" t="inlineStr"/>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>https://cardosoadvocacia.com.br/</t>
+          <t>https://www.delgadoazevedo.com.br/</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>Tel (71) 99695-0180 / (71) 3034-3159 | Sede Salvador/BA + unidade Pinheiros, Sao Paulo/SP | CNPJ 15.176.644/0001-02 | OAB/BA 2056/2011</t>
+          <t>Tel (61) 99955-8009 | Gabriel Espindola de Souza OAB-DF 71.982</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>Texto do site: "ATUAMOS NO BRASIL INTEIRO - estamos presentes em MAIS DE 21 ESTADOS". Planos de saude. Operacao nacional a distancia precisa de gente nas comarcas.</t>
+          <t>Declaram ATUACAO NACIONAL e atendimento 24 horas, em todos os tribunais do Brasil. Liminar, home care, negativa de medicamento e internacao - teses que voce ja domina.</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -4374,17 +4374,17 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Delgado Azevedo Advogados</t>
+          <t>GAMAA - Advocacia de Bancos &amp; Empresas</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Brasília</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -4394,28 +4394,28 @@
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>contato@delgadoazevedo.com.br</t>
+          <t>contato@gamaa.com.br</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em saude nas comarcas de RO</t>
+          <t>Parceria e correspondencia em RO</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>https://www.delgadoazevedo.com.br/</t>
+          <t>https://gamaa.com.br/</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Tel (61) 99955-8009 | Gabriel Espindola de Souza OAB-DF 71.982</t>
+          <t>Tel (31) 3274-9120 | R. Sao Paulo, 1071, 10o andar, Bloco B, Centro, BH/MG | Gilberto Miranda (proprietario)</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>Declaram ATUACAO NACIONAL e atendimento 24 horas, em todos os tribunais do Brasil. Liminar, home care, negativa de medicamento e internacao - teses que voce ja domina.</t>
+          <t>TEXTO DO PROPRIO SITE: "firmou parcerias com diversos escritorios de advogados do pais e POSSUI VARIOS CORRESPONDENTES no interior do estado de Minas Gerais". Ja usam o modelo. Clientes: Santander, Azul, BRF, Danone, Pernambucanas, Leroy Merlin. Tem pagina PARCEIROS.</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4432,17 +4432,17 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>GAMAA - Advocacia de Bancos &amp; Empresas</t>
+          <t>Gantus Advogados Associados</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Belo Horizonte</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -4452,28 +4452,28 @@
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>contato@gamaa.com.br</t>
+          <t>contato@gantusadvogados.com.br</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>Parceria e correspondencia em RO</t>
+          <t>Correspondencia para a carteira de massa em RO</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>https://gamaa.com.br/</t>
+          <t>https://gantusadvogados.com.br/</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>Tel (31) 3274-9120 | R. Sao Paulo, 1071, 10o andar, Bloco B, Centro, BH/MG | Gilberto Miranda (proprietario)</t>
+          <t>Tel (11) 94924-8141 / (11) 3813-5211 | Alameda Joaquim Eugenio de Lima, 696, Jardins, Sao Paulo/SP | Filial em Brasilia/DF | Fundador: Guilherme Miguel Gantus</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>TEXTO DO PROPRIO SITE: "firmou parcerias com diversos escritorios de advogados do pais e POSSUI VARIOS CORRESPONDENTES no interior do estado de Minas Gerais". Ja usam o modelo. Clientes: Santander, Azul, BRF, Danone, Pernambucanas, Leroy Merlin. Tem pagina PARCEIROS.</t>
+          <t>Area declarada de CONTENCIOSO DE MASSA e atuacao em TODO O TERRITORIO NACIONAL com apenas duas sedes (SP e DF). Dependem de correspondente fora do eixo.</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4490,17 +4490,17 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Gantus Advogados Associados</t>
+          <t>Gilmar Araujo da Costa Advocacia</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Manaus</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -4510,28 +4510,28 @@
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>contato@gantusadvogados.com.br</t>
+          <t>gac.advogado89@gmail.com</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia para a carteira de massa em RO</t>
+          <t>Correspondencia em RO - consumidor e bancario</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>https://gantusadvogados.com.br/</t>
+          <t>https://gilmararaujoadvocacia.com.br/</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Tel (11) 94924-8141 / (11) 3813-5211 | Alameda Joaquim Eugenio de Lima, 696, Jardins, Sao Paulo/SP | Filial em Brasilia/DF | Fundador: Guilherme Miguel Gantus</t>
+          <t>Tel (92) 98441-1276 | R. Rio Tarauaca, 36, Nossa Sra. das Gracas, Manaus-AM | CNPJ 46.366.996/0001-54</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>Area declarada de CONTENCIOSO DE MASSA e atuacao em TODO O TERRITORIO NACIONAL com apenas duas sedes (SP e DF). Dependem de correspondente fora do eixo.</t>
+          <t>Atuacao declarada EM TODO O BRASIL em consumidor e bancario: cartao RMC, consignado nao solicitado, juros abusivos, negativacao indevida. Mesmas teses que voce domina. Regiao Norte.</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4548,17 +4548,17 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Gilmar Araujo da Costa Advocacia</t>
+          <t>LDCM Advogados</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -4568,28 +4568,28 @@
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>gac.advogado89@gmail.com</t>
+          <t>contato@ldcm.com.br</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em RO - consumidor e bancario</t>
+          <t>Correspondencia para carteiras de bancario, telecom e varejo</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>https://gilmararaujoadvocacia.com.br/</t>
+          <t>https://www.ldcm.com.br/</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>Tel (92) 98441-1276 | R. Rio Tarauaca, 36, Nossa Sra. das Gracas, Manaus-AM | CNPJ 46.366.996/0001-54</t>
+          <t>Tel RJ +55 21 3500-3990 | SP +55 11 4380-8626 | Av. Epitacio Pessoa, 1.274, Ipanema, RJ | Av. Brig. Faria Lima, 4.300, Vila Olimpia, SP | E-mail nominal publicado: bruno.barreto@ldcm.com.br</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>Atuacao declarada EM TODO O BRASIL em consumidor e bancario: cartao RMC, consignado nao solicitado, juros abusivos, negativacao indevida. Mesmas teses que voce domina. Regiao Norte.</t>
+          <t>Boutique de disputas com carteira declarada em bancario, telecomunicacoes e varejo - os tres setores de maior contencioso de massa. So duas pracas.</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4606,17 +4606,17 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>LDCM Advogados</t>
+          <t>Marcelo Tostes Advogados - contato geral</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -4626,28 +4626,28 @@
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>contato@ldcm.com.br</t>
+          <t>contato@mtostes.com.br</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia para carteiras de bancario, telecom e varejo</t>
+          <t>Correspondencia em RO / candidatura</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ldcm.com.br/</t>
+          <t>https://mtostes.com.br/</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Tel RJ +55 21 3500-3990 | SP +55 11 4380-8626 | Av. Epitacio Pessoa, 1.274, Ipanema, RJ | Av. Brig. Faria Lima, 4.300, Vila Olimpia, SP | E-mail nominal publicado: bruno.barreto@ldcm.com.br</t>
+          <t>Unidades e telefones: SP (11) 4837-3400, BH (31) 4501-4100, Porto Alegre (51) 3103-4901, Vitoria (27) 3345-1999, Brasilia (61) 3225-4774, Rio de Janeiro, Florianopolis</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>Boutique de disputas com carteira declarada em bancario, telecomunicacoes e varejo - os tres setores de maior contencioso de massa. So duas pracas.</t>
+          <t>SEGUNDO E-MAIL da banca (o outro e recrutamento@mtostes.com.br). Area declarada "Contencioso Escala" e "Service, Backoffice &amp; Gestao de Dados". Nenhuma unidade no Norte.</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4664,17 +4664,17 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Marcelo Tostes Advogados - contato geral</t>
+          <t>Nelson Wilians Advogados (NWADV) - fundador</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Belo Horizonte</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -4684,28 +4684,28 @@
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>contato@mtostes.com.br</t>
+          <t>nelson@nwadv.com.br</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em RO / candidatura</t>
+          <t>Correspondencia / associacao - maior banca do pais</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>https://mtostes.com.br/</t>
+          <t>https://www.nwadv.com.br/</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>Unidades e telefones: SP (11) 4837-3400, BH (31) 4501-4100, Porto Alegre (51) 3103-4901, Vitoria (27) 3345-1999, Brasilia (61) 3225-4774, Rio de Janeiro, Florianopolis</t>
+          <t>Tel SP (11) 3330-2299 | Unidades com telefone proprio em TODOS os estados, incluindo RONDONIA | Manaus (92) 3659-3954, Rio Branco (68) 3222-8576, Macapa (96) 3224-1169, Brasilia (61) 3106-2000</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>SEGUNDO E-MAIL da banca (o outro e recrutamento@mtostes.com.br). Area declarada "Contencioso Escala" e "Service, Backoffice &amp; Gestao de Dados". Nenhuma unidade no Norte.</t>
+          <t>E-MAIL DO PROPRIO FUNDADOR publicado no site. Declaram PRESENCA FISICA EM TODOS OS ESTADOS BRASILEIROS. Ja tem unidade em Porto Velho - o encaixe aqui e cobrir as comarcas do INTERIOR de RO, onde a unidade da capital nao chega.</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Nelson Wilians Advogados (NWADV) - fundador</t>
+          <t>Parra Advogados</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -4742,28 +4742,28 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>nelson@nwadv.com.br</t>
+          <t>contato@parraadvogados.com.br</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia / associacao - maior banca do pais</t>
+          <t>Correspondencia em saude e securitario em RO</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>https://www.nwadv.com.br/</t>
+          <t>https://www.parraadvogados.com.br/</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Tel SP (11) 3330-2299 | Unidades com telefone proprio em TODOS os estados, incluindo RONDONIA | Manaus (92) 3659-3954, Rio Branco (68) 3222-8576, Macapa (96) 3224-1169, Brasilia (61) 3106-2000</t>
+          <t>Tel (11) 2092-8728 / (11) 94529-1615 | R. Nova Jerusalem, 740, sala 1, Chacara Santo Antonio, Sao Paulo/SP | OAB/SP 18.155</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>E-MAIL DO PROPRIO FUNDADOR publicado no site. Declaram PRESENCA FISICA EM TODOS OS ESTADOS BRASILEIROS. Ja tem unidade em Porto Velho - o encaixe aqui e cobrir as comarcas do INTERIOR de RO, onde a unidade da capital nao chega.</t>
+          <t>ENCAIXE PERFEITO: o site diz que prestam servico "com atendimento em TODO BRASIL, presencial ou virtual, MEDIANTE CONTRATACAO POR SERVICO ou assessoria mensal". E o modelo de correspondente descrito com outras palavras. Especialistas em liminares contra planos de saude - sua area.</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Parra Advogados</t>
+          <t>R. Barreto Advogados</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -4800,28 +4800,28 @@
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>contato@parraadvogados.com.br</t>
+          <t>rbarreto@rbarreto.adv.br</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia em saude e securitario em RO</t>
+          <t>Correspondencia e audiencias em RO</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>https://www.parraadvogados.com.br/</t>
+          <t>https://www.rbarreto.adv.br/</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>Tel (11) 2092-8728 / (11) 94529-1615 | R. Nova Jerusalem, 740, sala 1, Chacara Santo Antonio, Sao Paulo/SP | OAB/SP 18.155</t>
+          <t>Tel (11) 3044-2293 | Av. Nove de Julho, 4254, Jardim Paulista, Sao Paulo/SP</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>ENCAIXE PERFEITO: o site diz que prestam servico "com atendimento em TODO BRASIL, presencial ou virtual, MEDIANTE CONTRATACAO POR SERVICO ou assessoria mensal". E o modelo de correspondente descrito com outras palavras. Especialistas em liminares contra planos de saude - sua area.</t>
+          <t>Numeros do proprio site: +22.000 acoes contrarias, +4.000 processos de recuperacao de credito, R$ 80 milhoes recuperados. ATENDEM TODO O BRASIL DE FORMA REMOTA - precisam de gente em campo nas comarcas.</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -4838,17 +4838,17 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>R. Barreto Advogados</t>
+          <t>Ribeiro &amp; Feitoza Advogados</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Manaus</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -4858,28 +4858,28 @@
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>rbarreto@rbarreto.adv.br</t>
+          <t>contato@ribeiroefeitozaadvogados.com</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia e audiencias em RO</t>
+          <t>Parceria e correspondencia na regiao Norte</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>https://www.rbarreto.adv.br/</t>
+          <t>https://ribeiroefeitozaadvogados.com.br/</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Tel (11) 3044-2293 | Av. Nove de Julho, 4254, Jardim Paulista, Sao Paulo/SP</t>
+          <t>Tel +55 92 99147-9179 | Avenida Getulio Vargas, 1222, Centro, Manaus/AM</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Numeros do proprio site: +22.000 acoes contrarias, +4.000 processos de recuperacao de credito, R$ 80 milhoes recuperados. ATENDEM TODO O BRASIL DE FORMA REMOTA - precisam de gente em campo nas comarcas.</t>
+          <t>12 anos, referencia no Amazonas. Atuam em consumidor, bancario, licitacoes e ESG. Regiao Norte - logistica e cultura processual iguais as de RO.</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -4896,17 +4896,17 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Ribeiro &amp; Feitoza Advogados</t>
+          <t>SSantos Advogados</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -4916,28 +4916,28 @@
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>contato@ribeiroefeitozaadvogados.com</t>
+          <t>advocacia@ssantos.adv.br</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Parceria e correspondencia na regiao Norte</t>
+          <t>Correspondencia previdenciaria em RO</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>https://ribeiroefeitozaadvogados.com.br/</t>
+          <t>https://ssantos.adv.br/</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>Tel +55 92 99147-9179 | Avenida Getulio Vargas, 1222, Centro, Manaus/AM</t>
+          <t>(41) 3023-1498 principal | (41) 98850-9639 comercial | Rua Emiliano Perneta, 680, 5o andar, Centro, Curitiba-PR</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>12 anos, referencia no Amazonas. Atuam em consumidor, bancario, licitacoes e ESG. Regiao Norte - logistica e cultura processual iguais as de RO.</t>
+          <t>Presenca fisica em 6 ESTADOS (PR, SP, ES, BA, SP-Santos) e parceiros estrategicos em outros. 23 anos em revisao de aposentadoria. Parceria com +10 associacoes de aposentados. Norte descoberto.</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -4954,17 +4954,17 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>SSantos Advogados</t>
+          <t>Tomás de Souza Sociedade de Advocacia</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Brasília</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -4974,28 +4974,28 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>advocacia@ssantos.adv.br</t>
+          <t>tomasdesouzaadvogados@gmail.com</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia previdenciaria em RO</t>
+          <t>Entrar na rede de advogados associados</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>https://ssantos.adv.br/</t>
+          <t>https://tomasdesouzaadvogados.com.br/</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>(41) 3023-1498 principal | (41) 98850-9639 comercial | Rua Emiliano Perneta, 680, 5o andar, Centro, Curitiba-PR</t>
+          <t>Tel (61) 99221-1401 | Sede: SMPW Q22, Cj 01, Lote 07, Casa B, Park Way, Brasilia/DF | Unidade: Rua 122, 216, Setor Sul, Goiania/GO</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>Presenca fisica em 6 ESTADOS (PR, SP, ES, BA, SP-Santos) e parceiros estrategicos em outros. 23 anos em revisao de aposentadoria. Parceria com +10 associacoes de aposentados. Norte descoberto.</t>
+          <t>TEXTO DO SITE: atuam "com o APOIO DE UMA REDE DE ADVOGADOS ASSOCIADOS". Ja operam no modelo. Atuacao em tribunais superiores e Justica Federal. So duas pracas.</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -5012,17 +5012,17 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Tomás de Souza Sociedade de Advocacia</t>
+          <t>Trajano Neto &amp; Paciornik Advogados (TNP)</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Brasília</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -5032,28 +5032,28 @@
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>tomasdesouzaadvogados@gmail.com</t>
+          <t>contato@tnp.adv.br</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Entrar na rede de advogados associados</t>
+          <t>Correspondencia na rede de coligados - comarcas de RO</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>https://tomasdesouzaadvogados.com.br/</t>
+          <t>https://tnp.adv.br/novosite/gestao-do-contencioso-de-massa/</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>Tel (61) 99221-1401 | Sede: SMPW Q22, Cj 01, Lote 07, Casa B, Park Way, Brasilia/DF | Unidade: Rua 122, 216, Setor Sul, Goiania/GO</t>
+          <t>0800 575 0011 | +55 41 3075-5020 | Euripedes Garcez do Nascimento, 549, Ahu, Curitiba/PR</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>TEXTO DO SITE: atuam "com o APOIO DE UMA REDE DE ADVOGADOS ASSOCIADOS". Ja operam no modelo. Atuacao em tribunais superiores e Justica Federal. So duas pracas.</t>
+          <t>ALVO NUMERO 1 DE CORRESPONDENCIA: area declarada de GESTAO DO CONTENCIOSO DE MASSA operando com "REDE DE COLIGADOS EM TODO BRASIL". Unidades: Brasilia, Natal, Sao Luis, Guarapuava, Florianopolis, Sao Paulo, Fortaleza - NENHUMA NO NORTE. Rondonia e buraco na malha deles.</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -5070,17 +5070,17 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Trajano Neto &amp; Paciornik Advogados (TNP)</t>
+          <t>Ultreia Contábil</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Brasília</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -5090,28 +5090,28 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>contato@tnp.adv.br</t>
+          <t>assessoria@ultreiacontabil.com.br</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia na rede de coligados - comarcas de RO</t>
+          <t>Parceria contabil-juridica</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>https://tnp.adv.br/novosite/gestao-do-contencioso-de-massa/</t>
+          <t>https://ultreiacontabil.com.br/</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>0800 575 0011 | +55 41 3075-5020 | Euripedes Garcez do Nascimento, 549, Ahu, Curitiba/PR</t>
+          <t>Tel (61) 99694-5756</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>ALVO NUMERO 1 DE CORRESPONDENCIA: area declarada de GESTAO DO CONTENCIOSO DE MASSA operando com "REDE DE COLIGADOS EM TODO BRASIL". Unidades: Brasilia, Natal, Sao Luis, Guarapuava, Florianopolis, Sao Paulo, Fortaleza - NENHUMA NO NORTE. Rondonia e buraco na malha deles.</t>
+          <t>ATENDE ADVOGADOS como especialidade declarada, e faz Planejamento e Recuperacao Tributaria - parceria natural na sua area tributaria.</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -5128,48 +5128,48 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Ultreia Contábil</t>
+          <t>Amil</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Brasília</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>assessoria@ultreiacontabil.com.br</t>
+          <t>0800 721 1094</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Parceria contabil-juridica</t>
+          <t>Contencioso de saude suplementar</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>https://ultreiacontabil.com.br/</t>
+          <t>https://www.amil.com.br/</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>Tel (61) 99694-5756</t>
+          <t>Ouvidoria: 3004-1094 (capitais) e 0800 721 1094 (demais localidades) | Av. Dr. Chucri Zaidan, 1649, Ed. EZ Towers, Torre B, 23o andar, Sao Paulo/SP</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>ATENDE ADVOGADOS como especialidade declarada, e faz Planejamento e Recuperacao Tributaria - parceria natural na sua area tributaria.</t>
+          <t>Operadora que mais cresceu em marco de 2026. Carteira nacional com contencioso disperso.</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Amil</t>
+          <t>Bocchi Advogados Associados</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Ribeirão Preto</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -5206,28 +5206,28 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>0800 721 1094</t>
+          <t>0800 000 3373</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Contencioso de saude suplementar</t>
+          <t>Correspondencia previdenciaria em RO</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>https://www.amil.com.br/</t>
+          <t>https://bocchiadvogados.com.br/</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Ouvidoria: 3004-1094 (capitais) e 0800 721 1094 (demais localidades) | Av. Dr. Chucri Zaidan, 1649, Ed. EZ Towers, Torre B, 23o andar, Sao Paulo/SP</t>
+          <t>Rua Amador Bueno, 800, Ribeirao Preto/SP</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>Operadora que mais cresceu em marco de 2026. Carteira nacional com contencioso disperso.</t>
+          <t>50+ anos em previdenciario, trabalhista e civel. Texto do site: "fornecemos servicos juridicos para clientes de TODO BRASIL E DO MUNDO". Uma sede so - dependem de apoio local.</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -5244,17 +5244,17 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Bocchi Advogados Associados</t>
+          <t>Escobar Advogados - Programa de Parcerias</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Ribeirão Preto</t>
+          <t>Goiânia</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -5264,28 +5264,28 @@
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>0800 000 3373</t>
+          <t>(62) 3280-9271</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia previdenciaria em RO</t>
+          <t>Programa de parcerias previdenciario</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>https://bocchiadvogados.com.br/</t>
+          <t>https://escobaradvogados.com/parcerias/</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>Rua Amador Bueno, 800, Ribeirao Preto/SP</t>
+          <t>Responsavel: Dra. Ana Lara | Parceiro recebe relatorios mensais e reunioes trimestrais</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>50+ anos em previdenciario, trabalhista e civel. Texto do site: "fornecemos servicos juridicos para clientes de TODO BRASIL E DO MUNDO". Uma sede so - dependem de apoio local.</t>
+          <t>ATENCAO: 1a fase limitada a GOIAS, expansao nacional prevista para a 2a etapa. Vale registrar interesse agora para entrar na expansao. Foco em beneficios do INSS.</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -5302,17 +5302,17 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Escobar Advogados - Programa de Parcerias</t>
+          <t>Hapvida NotreDame Intermédica</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Goiânia</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -5322,28 +5322,28 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>(62) 3280-9271</t>
+          <t>0800 280 9130</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Programa de parcerias previdenciario</t>
+          <t>Contencioso de saude suplementar</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>https://escobaradvogados.com/parcerias/</t>
+          <t>https://www.hapvida.com.br/</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Responsavel: Dra. Ana Lara | Parceiro recebe relatorios mensais e reunioes trimestrais</t>
+          <t>0800 280 9130 (Norte e Nordeste) | 0800 018 3456 (Sul, Sudeste e Centro-Oeste) | Av. Heraclito Graca, 406, Centro, Fortaleza/CE | CNPJ 44.649.812/0001-38 | Tem TRABALHE CONOSCO e CANAL DE DENUNCIAS</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>ATENCAO: 1a fase limitada a GOIAS, expansao nacional prevista para a 2a etapa. Vale registrar interesse agora para entrar na expansao. Foco em beneficios do INSS.</t>
+          <t>Lider nacional em saude suplementar (8,8 milhoes de usuarios). Repare que tem 0800 ESPECIFICO para Norte e Nordeste - a operacao no Norte e separada.</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -5360,17 +5360,17 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Hapvida NotreDame Intermédica</t>
+          <t>Medina, Ribeiro &amp; Aguiar Advogados (MRA)</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Manaus</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -5380,28 +5380,28 @@
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>0800 280 9130</t>
+          <t>(92) 3242-0464</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Contencioso de saude suplementar</t>
+          <t>Correspondencia na regiao Norte</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>https://www.hapvida.com.br/</t>
+          <t>https://www.medinaeribeiro.com/</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>0800 280 9130 (Norte e Nordeste) | 0800 018 3456 (Sul, Sudeste e Centro-Oeste) | Av. Heraclito Graca, 406, Centro, Fortaleza/CE | CNPJ 44.649.812/0001-38 | Tem TRABALHE CONOSCO e CANAL DE DENUNCIAS</t>
+          <t>Forum Business Center, Sala 1702, Av. Andre Araujo, 97, Adrianopolis, Manaus/AM</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Lider nacional em saude suplementar (8,8 milhoes de usuarios). Repare que tem 0800 ESPECIFICO para Norte e Nordeste - a operacao no Norte e separada.</t>
+          <t>Full service empresarial no Amazonas, consultivo e contencioso. Regiao Norte.</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -5418,17 +5418,17 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Medina, Ribeiro &amp; Aguiar Advogados (MRA)</t>
+          <t>RS Advocacia Previdenciária (Ribeiro e Silva)</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -5438,28 +5438,28 @@
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>(92) 3242-0464</t>
+          <t>(11) 4210-0217</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia na regiao Norte</t>
+          <t>Correspondencia previdenciaria em RO</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>https://www.medinaeribeiro.com/</t>
+          <t>https://rsadvocaciaprevidenciaria.com.br/</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Forum Business Center, Sala 1702, Av. Andre Araujo, 97, Adrianopolis, Manaus/AM</t>
+          <t>Telefone e WhatsApp (11) 4210-0217 | Av. Paulista, 1.106, 16o andar, Sala 1 | Unidade Mooca: Rua Ipanema, 80 | CNPJ 55.065.755/0001-10</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Full service empresarial no Amazonas, consultivo e contencioso. Regiao Norte.</t>
+          <t>Atuam desde 2012 so em previdenciario, com CONSULTA ONLINE PARA TODO O BRASIL. BPC/LOAS, incapacidade, pensao por morte e revisoes - demandas do JEF de Ji-Parana.</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>RS Advocacia Previdenciária (Ribeiro e Silva)</t>
+          <t>SA Law Advogados</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -5496,28 +5496,28 @@
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>(11) 4210-0217</t>
+          <t>+55 (11) 3288-6060</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia previdenciaria em RO</t>
+          <t>Correspondencia e candidatura (pagina Careers)</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>https://rsadvocaciaprevidenciaria.com.br/</t>
+          <t>https://salaw.com.br/</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>Telefone e WhatsApp (11) 4210-0217 | Av. Paulista, 1.106, 16o andar, Sala 1 | Unidade Mooca: Rua Ipanema, 80 | CNPJ 55.065.755/0001-10</t>
+          <t>SP: Av. Brig. Faria Lima, 3311, 3o andar, (11) 3288-6060 | RJ: Av. Rio Branco, 151, 5o andar, (21) 3553-1707</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Atuam desde 2012 so em previdenciario, com CONSULTA ONLINE PARA TODO O BRASIL. BPC/LOAS, incapacidade, pensao por morte e revisoes - demandas do JEF de Ji-Parana.</t>
+          <t>Tem pagina CAREERS. Area declarada de Strategic Litigation and Arbitration.</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -5534,17 +5534,17 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>SA Law Advogados</t>
+          <t>Select Saúde (Select Operadora)</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Goiânia</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -5554,28 +5554,28 @@
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>+55 (11) 3288-6060</t>
+          <t>0800 224 2808</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia e candidatura (pagina Careers)</t>
+          <t>Contencioso de saude suplementar</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>https://salaw.com.br/</t>
+          <t>https://selectoperadora.com.br/</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>SP: Av. Brig. Faria Lima, 3311, 3o andar, (11) 3288-6060 | RJ: Av. Rio Branco, 151, 5o andar, (21) 3553-1707</t>
+          <t>St. Oeste, Goiania-GO</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Tem pagina CAREERS. Area declarada de Strategic Litigation and Arbitration.</t>
+          <t>TEM PAGINA "SEJA UM CREDENCIADO" E "SEJA NOSSO PARCEIRO" - canais formais de entrada. Opera em Porto Velho e Ji-Parana.</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -5592,17 +5592,17 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Select Saúde (Select Operadora)</t>
+          <t>Zveiter Advogados</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Goiânia</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -5612,28 +5612,28 @@
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>0800 224 2808</t>
+          <t>55 (21) 3380-1155</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Contencioso de saude suplementar</t>
+          <t>Correspondencia para as carteiras de massa</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>https://selectoperadora.com.br/</t>
+          <t>https://zveiter.com.br/</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>St. Oeste, Goiania-GO</t>
+          <t>Av. Presidente Antonio Carlos, 51, 19o e 20o andares, Centro, Rio de Janeiro/RJ | Fundado em 1957</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>TEM PAGINA "SEJA UM CREDENCIADO" E "SEJA NOSSO PARCEIRO" - canais formais de entrada. Opera em Porto Velho e Ji-Parana.</t>
+          <t>67 anos. Atua em contencioso de massa, saude suplementar, recuperacao judicial e falencias. Conduz as RJs do Grupo Petropolis e Grupo Americanas - carteiras com credores no pais inteiro.</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -5650,48 +5650,48 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Zveiter Advogados</t>
+          <t>ABL Advogados (Aith, Badari e Luchin)</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Santo André</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>TELEFONE</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>55 (21) 3380-1155</t>
+          <t>https://abladvogados.com/</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia para as carteiras de massa</t>
+          <t>Parceria previdenciaria - pagina PARA ADVOGADOS</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>https://zveiter.com.br/</t>
+          <t>https://abladvogados.com/</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Av. Presidente Antonio Carlos, 51, 19o e 20o andares, Centro, Rio de Janeiro/RJ | Fundado em 1957</t>
+          <t>Matriz Santo Andre/SP (11) 4509-4697 | filiais: Piracaia, Extrema/MG, Rio Claro 0800 707 4697, Mogi Mirim, Santos, Atibaia, Assis, Estiva Gerbi</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>67 anos. Atua em contencioso de massa, saude suplementar, recuperacao judicial e falencias. Conduz as RJs do Grupo Petropolis e Grupo Americanas - carteiras com credores no pais inteiro.</t>
+          <t>TEM MENU "PARA ADVOGADOS" E "TRABALHE CONOSCO" - canal especifico para parceria entre advogados. +90 profissionais so em previdenciario. Todas as filiais no Sudeste - Norte descoberto.</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -5708,17 +5708,17 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>ABL Advogados (Aith, Badari e Luchin)</t>
+          <t>Brasdiesel (Concessionária Scania)</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Santo André</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
@@ -5728,28 +5728,28 @@
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>https://abladvogados.com/</t>
+          <t>https://www.brasdiesel.com.br/</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Parceria previdenciaria - pagina PARA ADVOGADOS</t>
+          <t>Assessoria em consumidor e contratos</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>https://abladvogados.com/</t>
+          <t>https://www.brasdiesel.com.br/</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>Matriz Santo Andre/SP (11) 4509-4697 | filiais: Piracaia, Extrema/MG, Rio Claro 0800 707 4697, Mogi Mirim, Santos, Atibaia, Assis, Estiva Gerbi</t>
+          <t>Paginas: Fale Conosco, TRABALHE CONOSCO, Vagas Disponiveis e COMPLIANCE BRASDIESEL</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>TEM MENU "PARA ADVOGADOS" E "TRABALHE CONOSCO" - canal especifico para parceria entre advogados. +90 profissionais so em previdenciario. Todas as filiais no Sudeste - Norte descoberto.</t>
+          <t>ATENCAO: este dominio e da concessionaria Scania, pode nao ser a TRR BrasDiesel de Ji-Parana do ranking Econodata - confirmar antes de abordar. Tem canal de compliance e vagas.</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -5766,17 +5766,17 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Brasdiesel (Concessionária Scania)</t>
+          <t>Energisa (grupo)</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Cataguases</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
@@ -5786,28 +5786,28 @@
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>https://www.brasdiesel.com.br/</t>
+          <t>https://www.energisa.com.br/</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Assessoria em consumidor e contratos</t>
+          <t>Defesa em acoes consumeristas nas comarcas de RO</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>https://www.brasdiesel.com.br/</t>
+          <t>https://www.energisa.com.br/</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Paginas: Fale Conosco, TRABALHE CONOSCO, Vagas Disponiveis e COMPLIANCE BRASDIESEL</t>
+          <t>Site institucional lista atuacao em RONDONIA entre os estados atendidos, com acoes em Porto Velho e JI-PARANA</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>ATENCAO: este dominio e da concessionaria Scania, pode nao ser a TRR BrasDiesel de Ji-Parana do ranking Econodata - confirmar antes de abordar. Tem canal de compliance e vagas.</t>
+          <t>Concessionaria de energia e um dos setores mais acionados por consumidores segundo o CNJ. Atuacao confirmada em Ji-Parana no proprio site.</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -5824,17 +5824,17 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Energisa (grupo)</t>
+          <t>JBS</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Cataguases</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
@@ -5844,28 +5844,28 @@
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>https://www.energisa.com.br/</t>
+          <t>https://www.jbs.com.br/</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Defesa em acoes consumeristas nas comarcas de RO</t>
+          <t>Assessoria trabalhista e doencas ocupacionais</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>https://www.energisa.com.br/</t>
+          <t>https://www.jbs.com.br/</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>Site institucional lista atuacao em RONDONIA entre os estados atendidos, com acoes em Porto Velho e JI-PARANA</t>
+          <t>+158 mil colaboradores no Brasil | +130 fabricas | presenca em 17 estados | pagina CARREIRAS</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Concessionaria de energia e um dos setores mais acionados por consumidores segundo o CNJ. Atuacao confirmada em Ji-Parana no proprio site.</t>
+          <t>CINCO plantas em Rondonia (Vilhena, Sao Miguel do Guapore, Rolim de Moura, Ariquemes e Porto Velho). 158 mil empregados = passivo trabalhista e de doenca ocupacional em escala. Sua especialidade declarada.</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -5882,17 +5882,17 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JBS</t>
+          <t>Koetz Advocacia</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Porto Alegre</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
@@ -5902,28 +5902,28 @@
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>https://www.jbs.com.br/</t>
+          <t>https://koetzadvocacia.com.br/</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Assessoria trabalhista e doencas ocupacionais</t>
+          <t>Correspondencia previdenciaria em RO</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>https://www.jbs.com.br/</t>
+          <t>https://koetzadvocacia.com.br/</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>+158 mil colaboradores no Brasil | +130 fabricas | presenca em 17 estados | pagina CARREIRAS</t>
+          <t>Contato pelo site | Eduardo Koetz (fundador), Murilo Mella (CEO)</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>CINCO plantas em Rondonia (Vilhena, Sao Miguel do Guapore, Rolim de Moura, Ariquemes e Porto Velho). 158 mil empregados = passivo trabalhista e de doenca ocupacional em escala. Sua especialidade declarada.</t>
+          <t>"Atendemos ONLINE qualquer pessoa em QUALQUER LUGAR DO MUNDO". Aposentadoria complexa e internacional. Operacao 100% digital precisa de presenca fisica para pericia e audiencia no JEF.</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -5940,17 +5940,17 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Koetz Advocacia</t>
+          <t>Parish &amp; Zenandro Advogados</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Porto Alegre</t>
+          <t>Salvador</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
@@ -5960,28 +5960,28 @@
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>https://koetzadvocacia.com.br/</t>
+          <t>https://pz.adv.br/</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia previdenciaria em RO</t>
+          <t>Correspondencia previdenciaria e do servidor</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>https://koetzadvocacia.com.br/</t>
+          <t>https://pz.adv.br/</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>Contato pelo site | Eduardo Koetz (fundador), Murilo Mella (CEO)</t>
+          <t>Matriz Salvador: Rua Frederico Simoes, 153, 13o andar, Caminho das Arvores | Unidades: Serrinha, Monte Gordo/Camacari, Retirolandia, Sao Goncalo dos Campos, Santaluz, Camacari, Feira de Santana</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>"Atendemos ONLINE qualquer pessoa em QUALQUER LUGAR DO MUNDO". Aposentadoria complexa e internacional. Operacao 100% digital precisa de presenca fisica para pericia e audiencia no JEF.</t>
+          <t>88 PROFISSIONAIS na equipe juridica, todos concentrados na Bahia. Previdenciario, consumidor e trabalhista. Expansao para fora do estado exigiria parceiro local.</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -5998,17 +5998,17 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Parish &amp; Zenandro Advogados</t>
+          <t>Vitorino &amp; Murta Advogados</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>Manaus</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
@@ -6018,28 +6018,28 @@
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>https://pz.adv.br/</t>
+          <t>https://vitorinoemurta.com.br/</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia previdenciaria e do servidor</t>
+          <t>Correspondencia bancaria em RO</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>https://pz.adv.br/</t>
+          <t>https://vitorinoemurta.com.br/escritorio-em-manaus/</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Matriz Salvador: Rua Frederico Simoes, 153, 13o andar, Caminho das Arvores | Unidades: Serrinha, Monte Gordo/Camacari, Retirolandia, Sao Goncalo dos Campos, Santaluz, Camacari, Feira de Santana</t>
+          <t>Contato por WhatsApp pelo site | Escritorios em Manaus, Sao Paulo, Brasilia, Florianopolis e Vila Velha</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>88 PROFISSIONAIS na equipe juridica, todos concentrados na Bahia. Previdenciario, consumidor e trabalhista. Expansao para fora do estado exigiria parceiro local.</t>
+          <t>Maior banca de direito bancario do Norte. Atua em gestao de passivos bancarios e tributarios e execucao fiscal. Cinco pracas, nenhuma em RO.</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -6056,48 +6056,48 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Vitorino &amp; Murta Advogados</t>
+          <t>Jurídico Certo</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Manaus</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="E96" s="10" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>https://vitorinoemurta.com.br/</t>
+          <t>https://www.juridicocerto.com/cadastro-advogados-correspondentes-juridicos</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Correspondencia bancaria em RO</t>
+          <t>Cadastro como correspondente</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>https://vitorinoemurta.com.br/escritorio-em-manaus/</t>
+          <t>https://www.juridicocerto.com/cadastro-advogados-correspondentes-juridicos</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>Contato por WhatsApp pelo site | Escritorios em Manaus, Sao Paulo, Brasilia, Florianopolis e Vila Velha</t>
+          <t>Plano Premium a partir de R$ 49/mes (anual). Cadastro inicial pede nome, e-mail profissional e senha</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Maior banca de direito bancario do Norte. Atua em gestao de passivos bancarios e tributarios e execucao fiscal. Cinco pracas, nenhuma em RO.</t>
+          <t>Tem o "Juridico Pag", que garante previsibilidade de recebimento. Algoritmo encaminha demandas proximas da sua localizacao. App avisa nova demanda.</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -6107,55 +6107,55 @@
       </c>
     </row>
     <row r="97" ht="62" customHeight="1">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>4. BANCA NACIONAL — ofereça correspondência em RO</t>
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>5. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Jurídico Certo</t>
+          <t>Juridigital (Drive Digital)</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>https://www.juridicocerto.com/cadastro-advogados-correspondentes-juridicos</t>
+          <t>relacionamento@juridigital.com.br</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Cadastro como correspondente</t>
+          <t>Rede de BPO juridico e correspondencia</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>https://www.juridicocerto.com/cadastro-advogados-correspondentes-juridicos</t>
+          <t>https://www.juridigital.com.br/bpo-juridico/</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Plano Premium a partir de R$ 49/mes (anual). Cadastro inicial pede nome, e-mail profissional e senha</t>
+          <t>WhatsApp (31) 99362-8269 | Belo Horizonte/MG | CNPJ 28.407.867/0001-85</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Tem o "Juridico Pag", que garante previsibilidade de recebimento. Algoritmo encaminha demandas proximas da sua localizacao. App avisa nova demanda.</t>
+          <t>Produzem conteudo sobre BPO juridico E sobre contratacao de correspondente juridico - conhecem e intermediam os dois mercados. Base de escritorios clientes.</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -6172,48 +6172,48 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Juridigital (Drive Digital)</t>
+          <t>CSilva Sociedade de Advogados (BPO.CS)</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Belo Horizonte</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>FORMULARIO</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>relacionamento@juridigital.com.br</t>
+          <t>https://csilvaadv.com.br/terceirizacao-de-servicos-juridicos/</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Rede de BPO juridico e correspondencia</t>
+          <t>Prestacao de servico para a operacao de BPO</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>https://www.juridigital.com.br/bpo-juridico/</t>
+          <t>https://csilvaadv.com.br/terceirizacao-de-servicos-juridicos/</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>WhatsApp (31) 99362-8269 | Belo Horizonte/MG | CNPJ 28.407.867/0001-85</t>
+          <t>Contato via WhatsApp pelo site</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Produzem conteudo sobre BPO juridico E sobre contratacao de correspondente juridico - conhecem e intermediam os dois mercados. Base de escritorios clientes.</t>
+          <t>Escritorio especializado em BPO Juridico para empresas de todos os portes.</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -6230,17 +6230,17 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>CSilva Sociedade de Advogados (BPO.CS)</t>
+          <t>Carbonera &amp; Tomazini Advogados</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Gravataí</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
@@ -6250,28 +6250,28 @@
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>https://csilvaadv.com.br/terceirizacao-de-servicos-juridicos/</t>
+          <t>https://www.carboneraetomazini.com.br/</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Prestacao de servico para a operacao de BPO</t>
+          <t>PARCERIA EM DIREITO PREVIDENCIARIO (pagina propria)</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>https://csilvaadv.com.br/terceirizacao-de-servicos-juridicos/</t>
+          <t>https://www.carboneraetomazini.com.br/</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Contato via WhatsApp pelo site</t>
+          <t>Matriz Gravatai/RS (51) 3933-6733 | Filiais: Joinville (47) 3028-8555 e (47) 3017-5941, Rio Grande (53) 3035-3615, Fortaleza (85) 3032-4886 e (85) 3122-3878 | Escritorio Digital: (51) 3424-3615, (51) 99726-5382, (51) 99667-0941, (51) 99881-3738, (85) 98823-8227, (47) 98924-3140, (53) 99130-4900 | CNPJ 20.920.282/0001-52</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Escritorio especializado em BPO Juridico para empresas de todos os portes.</t>
+          <t>MELHOR ACHADO DA RODADA: o menu do site tem item proprio "PARCERIA EM DIREITO PREVIDENCIARIO" e tambem "Trabalhe Conosco". Atendem todo o Brasil pelo Escritorio Digital. OAB/RS 5.067 e OAB/SC 4.029. Previdenciario e sua area principal.</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -6288,17 +6288,17 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Carbonera &amp; Tomazini Advogados</t>
+          <t>Ehts Consulting</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Gravataí</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
@@ -6308,28 +6308,28 @@
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>https://www.carboneraetomazini.com.br/</t>
+          <t>https://ehts.com.br/quem-somos/</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>PARCERIA EM DIREITO PREVIDENCIARIO (pagina propria)</t>
+          <t>Prestacao de servico em legal operations</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>https://www.carboneraetomazini.com.br/</t>
+          <t>https://ehts.com.br/quem-somos/</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>Matriz Gravatai/RS (51) 3933-6733 | Filiais: Joinville (47) 3028-8555 e (47) 3017-5941, Rio Grande (53) 3035-3615, Fortaleza (85) 3032-4886 e (85) 3122-3878 | Escritorio Digital: (51) 3424-3615, (51) 99726-5382, (51) 99667-0941, (51) 99881-3738, (85) 98823-8227, (47) 98924-3140, (53) 99130-4900 | CNPJ 20.920.282/0001-52</t>
+          <t>Contato pelo site e WhatsApp</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>MELHOR ACHADO DA RODADA: o menu do site tem item proprio "PARCERIA EM DIREITO PREVIDENCIARIO" e tambem "Trabalhe Conosco". Atendem todo o Brasil pelo Escritorio Digital. OAB/RS 5.067 e OAB/SC 4.029. Previdenciario e sua area principal.</t>
+          <t>Top 10 LegalTech do Brasil (Ranking 100 Open Startups). Clientes: Petrobras, Porto Seguro, Eurofarma, Renner, Centauro, Nike, Airbnb. Legal Operations e Analytics Juridico - carteiras enormes que precisam de maos.</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -6346,17 +6346,17 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Ehts Consulting</t>
+          <t>Intelligenti Stefanini - Locação de Headcounts</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
@@ -6366,28 +6366,28 @@
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>https://ehts.com.br/quem-somos/</t>
+          <t>https://www.intelligenti.com.br/solucoes/bpo-juridico</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Prestacao de servico em legal operations</t>
+          <t>Alocacao como profissional juridico (headcount)</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>https://ehts.com.br/quem-somos/</t>
+          <t>https://www.intelligenti.com.br/solucoes/bpo-juridico</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>Contato pelo site e WhatsApp</t>
+          <t>Av. Eusebio Matoso, 1375, Sao Paulo/SP | Grupo Stefanini</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Top 10 LegalTech do Brasil (Ranking 100 Open Startups). Clientes: Petrobras, Porto Seguro, Eurofarma, Renner, Centauro, Nike, Airbnb. Legal Operations e Analytics Juridico - carteiras enormes que precisam de maos.</t>
+          <t>MODELO IDEAL PARA RENDA EXTRA: tem servico declarado de "LOCACAO DE HEADCOUNTS - acesso rapido e flexivel a profissionais qualificados do setor juridico". Eles alocam advogados sob demanda. Ofereca-se como headcount disponivel.</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -6404,17 +6404,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Intelligenti Stefanini - Locação de Headcounts</t>
+          <t>Lima &amp; Pegolo Advogados (LPADV)</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Não informado</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
@@ -6424,28 +6424,28 @@
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>https://www.intelligenti.com.br/solucoes/bpo-juridico</t>
+          <t>https://limaepegolo.com.br/seja-um-parceiro/</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Alocacao como profissional juridico (headcount)</t>
+          <t>Parceria com plataforma e teses prontas</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>https://www.intelligenti.com.br/solucoes/bpo-juridico</t>
+          <t>https://limaepegolo.com.br/seja-um-parceiro/</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Av. Eusebio Matoso, 1375, Sao Paulo/SP | Grupo Stefanini</t>
+          <t>Formulario na pagina "Seja um Parceiro"</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>MODELO IDEAL PARA RENDA EXTRA: tem servico declarado de "LOCACAO DE HEADCOUNTS - acesso rapido e flexivel a profissionais qualificados do setor juridico". Eles alocam advogados sob demanda. Ofereca-se como headcount disponivel.</t>
+          <t>MODELO INTERESSANTE: voce capta o cliente, eles assumem o trabalho tecnico. Texto do site: "uma vez validada a nova contratacao, TODO O TRABALHO SERA NOSSO". Da acesso a area restrita com teses do escritorio. Renda sem carga processual.</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Lima &amp; Pegolo Advogados (LPADV)</t>
+          <t>Souza Cruz Advogados - BPO Jurídico</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -6482,28 +6482,28 @@
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>https://limaepegolo.com.br/seja-um-parceiro/</t>
+          <t>https://souzacruz.adv.br/bpo-juridico/</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Parceria com plataforma e teses prontas</t>
+          <t>Prestacao de servico para a operacao de BPO trabalhista</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>https://limaepegolo.com.br/seja-um-parceiro/</t>
+          <t>https://souzacruz.adv.br/bpo-juridico/</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Formulario na pagina "Seja um Parceiro"</t>
+          <t>Contato pelo site com a Dra. Mariana Cruz</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>MODELO INTERESSANTE: voce capta o cliente, eles assumem o trabalho tecnico. Texto do site: "uma vez validada a nova contratacao, TODO O TRABALHO SERA NOSSO". Da acesso a area restrita com teses do escritorio. Renda sem carga processual.</t>
+          <t>BPO trabalhista que atende escritorios e departamentos juridicos: controladoria, gestao de prazos, acompanhamento processual, elaboracao de pecas e sustentacoes. Eles COMPRAM o servico que voce vende.</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -6513,60 +6513,64 @@
       </c>
     </row>
     <row r="104" ht="62" customHeight="1">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t>5. BPO / TERCEIRIZAÇÃO — ofereça seu serviço</t>
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>6. VAGA ABERTA — candidate-se</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Souza Cruz Advogados - BPO Jurídico</t>
+          <t>Carlos Miro Advogados</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Uberlândia</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="E104" s="10" t="inlineStr">
-        <is>
-          <t>FORMULARIO</t>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>https://souzacruz.adv.br/bpo-juridico/</t>
+          <t>yasminsantos@carlosmiro.adv.br</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>Prestacao de servico para a operacao de BPO trabalhista</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr"/>
+          <t>Advogado Contencioso Massificado</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>https://souzacruz.adv.br/bpo-juridico/</t>
+          <t>https://to.indeed.com/aanzcqdqkn8x</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>Contato pelo site com a Dra. Mariana Cruz</t>
+          <t>"Interessados na oportunidade podem se cadastrar por aqui ou enviar o curriculo para o e-mail yasminsantos@carlosmiro.adv.br"</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>BPO trabalhista que atende escritorios e departamentos juridicos: controladoria, gestao de prazos, acompanhamento processual, elaboracao de pecas e sustentacoes. Eles COMPRAM o servico que voce vende.</t>
+          <t>50 anos de mercado, bancario e empresarial. O anuncio diz que ja opera com CORRESPONDENTES em diversas localidades do pais - vale ofertar RO na mesma mensagem.</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>Site institucional (extracao Tavily)</t>
+          <t>Descricao completa da vaga no Indeed (get_job_details)</t>
         </is>
       </c>
     </row>
@@ -6578,17 +6582,17 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Carlos Miro Advogados</t>
+          <t>Carneiro &amp; Ramalho Consultoria (p/ NEST Construções)</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Uberlândia</t>
+          <t>Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -6598,32 +6602,32 @@
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>yasminsantos@carlosmiro.adv.br</t>
+          <t>consultoraselecaopb@gmail.com</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>Advogado Contencioso Massificado</t>
+          <t>Advogado(a) Associado(a)</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>https://to.indeed.com/aanzcqdqkn8x</t>
+          <t>https://to.indeed.com/aagvvpqgq4h9</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>"Interessados na oportunidade podem se cadastrar por aqui ou enviar o curriculo para o e-mail yasminsantos@carlosmiro.adv.br"</t>
+          <t>"Enviar o curriculo para o e-mail: consultoraselecaopb@gmail.com"</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>50 anos de mercado, bancario e empresarial. O anuncio diz que ja opera com CORRESPONDENTES em diversas localidades do pais - vale ofertar RO na mesma mensagem.</t>
+          <t>Civel, execucao e cobranca, audiencias.</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -6640,17 +6644,17 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Carneiro &amp; Ramalho Consultoria (p/ NEST Construções)</t>
+          <t>Décio Freire Advogados</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Jaboatão dos Guararapes</t>
+          <t>Teresina</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -6660,32 +6664,32 @@
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>consultoraselecaopb@gmail.com</t>
+          <t>christianedepaula@deciofreire.com.br</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>Advogado(a) Associado(a)</t>
+          <t>Advogado(a) Civel PLENO - Unidade Teresina (PJ)</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>https://to.indeed.com/aagvvpqgq4h9</t>
+          <t>https://to.indeed.com/aasphhw2vxx4</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>"Enviar o curriculo para o e-mail: consultoraselecaopb@gmail.com"</t>
+          <t>"Os(as) interessados(as) deverao encaminhar o curriculo informando a pretensao de honorarios para o e-mail christianedepaula@deciofreire.com.br"</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Civel, execucao e cobranca, audiencias.</t>
+          <t>Banca nacional com escritorios em SP, RJ, BH, Brasilia e Recife. Exige informar pretensao de honorarios. Contratacao PJ.</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -6702,17 +6706,17 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Décio Freire Advogados</t>
+          <t>GWF Advogados e Associados</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Teresina</t>
+          <t>Ribeirão Preto</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -6722,32 +6726,32 @@
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>christianedepaula@deciofreire.com.br</t>
+          <t>gestao@gwfadvocacia.com.br</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Advogado(a) Civel PLENO - Unidade Teresina (PJ)</t>
+          <t>Advogado(a) Senior Lider - Direito Bancario</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>https://to.indeed.com/aasphhw2vxx4</t>
+          <t>https://to.indeed.com/aa6ntjfd4f72</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>"Os(as) interessados(as) deverao encaminhar o curriculo informando a pretensao de honorarios para o e-mail christianedepaula@deciofreire.com.br"</t>
+          <t>"Interessados podem encaminhar o curriculo para: gestao@gwfadvocacia.com.br"</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Banca nacional com escritorios em SP, RJ, BH, Brasilia e Recife. Exige informar pretensao de honorarios. Contratacao PJ.</t>
+          <t>Bancario e contencioso civel. Faixa ate R$ 15.000.</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -6764,17 +6768,17 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>GWF Advogados e Associados</t>
+          <t>Gonçalves Júnior Advocacia</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Ribeirão Preto</t>
+          <t>Brasília</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -6784,32 +6788,32 @@
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>gestao@gwfadvocacia.com.br</t>
+          <t>contato@goncalvesjunioradv.com</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Advogado(a) Senior Lider - Direito Bancario</t>
+          <t>Advogado(a) Associado(a) - Civel/Tributario | ATUACAO INICIAL REMOTA</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>https://to.indeed.com/aa6ntjfd4f72</t>
+          <t>https://to.indeed.com/aaw8gpwjhqy7</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>"Interessados podem encaminhar o curriculo para: gestao@gwfadvocacia.com.br"</t>
+          <t>"Os interessados deverao enviar curriculo para: contato@goncalvesjunioradv.com - Assunto: Processo Seletivo - Advogado(a) Associado(a) - Civel/Tributario"</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Bancario e contencioso civel. Faixa ate R$ 15.000.</t>
+          <t>ATENCAO: o prazo do anuncio era 10/09/2026. Mas o proprio texto diz que aprovados ficam em cadastro por ate 6 meses - vale enviar assim mesmo.</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -6826,17 +6830,17 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Gonçalves Júnior Advocacia</t>
+          <t>Marcelo Tostes Advogados Associados</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Brasília</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -6846,32 +6850,32 @@
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>contato@goncalvesjunioradv.com</t>
+          <t>recrutamento@mtostes.com.br</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Advogado(a) Associado(a) - Civel/Tributario | ATUACAO INICIAL REMOTA</t>
+          <t>Advogado Civel Junior / Pleno - Contencioso de Escala</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>https://to.indeed.com/aaw8gpwjhqy7</t>
+          <t>https://to.indeed.com/aazhlrrjljqn</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>"Os interessados deverao enviar curriculo para: contato@goncalvesjunioradv.com - Assunto: Processo Seletivo - Advogado(a) Associado(a) - Civel/Tributario"</t>
+          <t>"Candidate-se ou envie seu curriculo para recrutamento@mtostes.com.br indicando no assunto Advogado Civel - BH"</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>ATENCAO: o prazo do anuncio era 10/09/2026. Mas o proprio texto diz que aprovados ficam em cadastro por ate 6 meses - vale enviar assim mesmo.</t>
+          <t>Banca nacional de contencioso de massa e recuperacao de credito. Colocar o assunto pedido.</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -6888,12 +6892,12 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Marcelo Tostes Advogados Associados</t>
+          <t>Reis Advogados Associados</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Belo Horizonte</t>
+          <t>Uberlândia</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -6901,19 +6905,19 @@
           <t>MG</t>
         </is>
       </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>PORTAL</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>recrutamento@mtostes.com.br</t>
+          <t>https://reisadvogados.vagas.solides.com.br/vaga/915401</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Advogado Civel Junior / Pleno - Contencioso de Escala</t>
+          <t>Assistente de Controladoria Juridica (PJ)</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -6923,17 +6927,17 @@
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>https://to.indeed.com/aazhlrrjljqn</t>
+          <t>https://to.indeed.com/aay7xrjqdxpw</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>"Candidate-se ou envie seu curriculo para recrutamento@mtostes.com.br indicando no assunto Advogado Civel - BH"</t>
+          <t>"REALIZAR CANDIDATURA NO LINK: https://reisadvogados.vagas.solides.com.br/vaga/915401"</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>Banca nacional de contencioso de massa e recuperacao de credito. Colocar o assunto pedido.</t>
+          <t>Candidatura so pelo link proprio, nao pelo Indeed.</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
@@ -6942,68 +6946,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="62" customHeight="1">
-      <c r="A111" s="12" t="inlineStr">
-        <is>
-          <t>6. VAGA ABERTA — candidate-se</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>Reis Advogados Associados</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>Uberlândia</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t>PORTAL</t>
-        </is>
-      </c>
-      <c r="F111" s="6" t="inlineStr">
-        <is>
-          <t>https://reisadvogados.vagas.solides.com.br/vaga/915401</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t>Assistente de Controladoria Juridica (PJ)</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t>https://to.indeed.com/aay7xrjqdxpw</t>
-        </is>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>"REALIZAR CANDIDATURA NO LINK: https://reisadvogados.vagas.solides.com.br/vaga/915401"</t>
-        </is>
-      </c>
-      <c r="K111" s="4" t="inlineStr">
-        <is>
-          <t>Candidatura so pelo link proprio, nao pelo Indeed.</t>
-        </is>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>Descricao completa da vaga no Indeed (get_job_details)</t>
-        </is>
-      </c>
-    </row>
+    <row r="111" ht="62" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:L111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
